--- a/assets/factor/Multiple Linear Regresion & FF3 - Students.xlsx
+++ b/assets/factor/Multiple Linear Regresion & FF3 - Students.xlsx
@@ -1,33 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18528"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philip\Dropbox\Courses\Teaching\FIN 203\FIN 203 Fall 2017\4 Multiple Linear Regression\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\4 Factor Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3687D6-C1C1-4C55-85FD-0CBD4A39B1EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="8226" activeTab="1" xr2:uid="{C20A87D4-BCEF-4287-8786-16E27E10B376}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{C20A87D4-BCEF-4287-8786-16E27E10B376}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="2" r:id="rId1"/>
     <sheet name="Returns" sheetId="1" r:id="rId2"/>
-    <sheet name="Replication" sheetId="4" r:id="rId3"/>
-    <sheet name="F-test" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Mkt</t>
   </si>
@@ -73,133 +78,15 @@
   <si>
     <t>Explanation</t>
   </si>
-  <si>
-    <t>Expected Return</t>
-  </si>
-  <si>
-    <t>Annualized</t>
-  </si>
-  <si>
-    <t>SUMMARY OUTPUT</t>
-  </si>
-  <si>
-    <t>Regression Statistics</t>
-  </si>
-  <si>
-    <t>R Square</t>
-  </si>
-  <si>
-    <t>Adjusted R Square</t>
-  </si>
-  <si>
-    <t>Standard Error</t>
-  </si>
-  <si>
-    <t>Observations</t>
-  </si>
-  <si>
-    <t>ANOVA</t>
-  </si>
-  <si>
-    <t>df</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Significance F</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>Residual</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Coefficients</t>
-  </si>
-  <si>
-    <t>t Stat</t>
-  </si>
-  <si>
-    <t>P-value</t>
-  </si>
-  <si>
-    <t>Lower 95%</t>
-  </si>
-  <si>
-    <t>Upper 95%</t>
-  </si>
-  <si>
-    <t>Intercept</t>
-  </si>
-  <si>
-    <t>Full: FF3</t>
-  </si>
-  <si>
-    <t>Reduced: CAPM</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>FF3:</t>
-  </si>
-  <si>
-    <t>MSE</t>
-  </si>
-  <si>
-    <t>SSE</t>
-  </si>
-  <si>
-    <t>CAPM:</t>
-  </si>
-  <si>
-    <t>F-stat</t>
-  </si>
-  <si>
-    <t>P-val</t>
-  </si>
-  <si>
-    <t>Conclusion</t>
-  </si>
-  <si>
-    <t>H0:</t>
-  </si>
-  <si>
-    <t>Ha:</t>
-  </si>
-  <si>
-    <t>Predicted</t>
-  </si>
-  <si>
-    <t>Error</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/yy"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -250,55 +137,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -310,7 +163,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -323,54 +176,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -691,25 +497,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C199B352-F1BA-4913-B187-0EA396EA65DC}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -720,7 +526,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -731,7 +537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -742,7 +548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -760,16 +566,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D3E3FF0-D3AD-48D6-988E-18EF1F03B3B4}">
-  <dimension ref="A1:M433"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:E433"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.1484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="8.796875" style="4"/>
-    <col min="9" max="9" width="12.94921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.796875" style="4"/>
+    <col min="1" max="1" width="5.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.75" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="3" t="s">
         <v>3</v>
@@ -783,28 +587,8 @@
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>29587</v>
       </c>
@@ -817,21 +601,11 @@
       <c r="D2" s="2">
         <v>0.03</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="2">
         <v>6.8499999999999991E-2</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>29618</v>
       </c>
@@ -844,33 +618,11 @@
       <c r="D3" s="2">
         <v>-3.0999999999999999E-3</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="2">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="10">
-        <f>J2*12</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="10">
-        <f t="shared" ref="K3:M3" si="0">K2*12</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>29646</v>
       </c>
@@ -883,17 +635,11 @@
       <c r="D4" s="2">
         <v>3.5799999999999998E-2</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="2">
         <v>6.5000000000000006E-3</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>29677</v>
       </c>
@@ -906,17 +652,11 @@
       <c r="D5" s="2">
         <v>4.4199999999999996E-2</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="2">
         <v>2.2599999999999999E-2</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>29707</v>
       </c>
@@ -929,17 +669,11 @@
       <c r="D6" s="2">
         <v>0.02</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="2">
         <v>-4.4000000000000003E-3</v>
       </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>29738</v>
       </c>
@@ -952,17 +686,11 @@
       <c r="D7" s="2">
         <v>-8.5000000000000006E-3</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="2">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="7"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>29768</v>
       </c>
@@ -975,17 +703,11 @@
       <c r="D8" s="2">
         <v>-2.1700000000000001E-2</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="2">
         <v>-6.3E-3</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>29799</v>
       </c>
@@ -998,17 +720,11 @@
       <c r="D9" s="2">
         <v>-1.95E-2</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="2">
         <v>4.8300000000000003E-2</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>29830</v>
       </c>
@@ -1021,17 +737,11 @@
       <c r="D10" s="2">
         <v>-2.6600000000000002E-2</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="2">
         <v>5.1799999999999999E-2</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>29860</v>
       </c>
@@ -1044,17 +754,11 @@
       <c r="D11" s="2">
         <v>2.1400000000000002E-2</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="2">
         <v>-4.2099999999999999E-2</v>
       </c>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>29891</v>
       </c>
@@ -1067,17 +771,11 @@
       <c r="D12" s="2">
         <v>-9.7000000000000003E-3</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="2">
         <v>1.89E-2</v>
       </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="7"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>29921</v>
       </c>
@@ -1090,17 +788,11 @@
       <c r="D13" s="2">
         <v>1.1699999999999999E-2</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="2">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>29952</v>
       </c>
@@ -1113,17 +805,11 @@
       <c r="D14" s="2">
         <v>-1.2800000000000001E-2</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="2">
         <v>3.1400000000000004E-2</v>
       </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="7"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>29983</v>
       </c>
@@ -1136,17 +822,11 @@
       <c r="D15" s="2">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="2">
         <v>6.0700000000000004E-2</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.6">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>30011</v>
       </c>
@@ -1159,17 +839,11 @@
       <c r="D16" s="2">
         <v>-2E-3</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="2">
         <v>3.78E-2</v>
       </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>30042</v>
       </c>
@@ -1182,17 +856,11 @@
       <c r="D17" s="2">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="2">
         <v>-2.81E-2</v>
       </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>30072</v>
       </c>
@@ -1205,17 +873,11 @@
       <c r="D18" s="2">
         <v>4.6999999999999993E-3</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="2">
         <v>1.8200000000000001E-2</v>
       </c>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>30103</v>
       </c>
@@ -1228,17 +890,11 @@
       <c r="D19" s="2">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="2">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>30133</v>
       </c>
@@ -1251,17 +907,11 @@
       <c r="D20" s="2">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="2">
         <v>1.5E-3</v>
       </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>30164</v>
       </c>
@@ -1274,17 +924,11 @@
       <c r="D21" s="2">
         <v>-4.0999999999999995E-2</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="2">
         <v>1.15E-2</v>
       </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>30195</v>
       </c>
@@ -1297,17 +941,11 @@
       <c r="D22" s="2">
         <v>2.8900000000000002E-2</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="2">
         <v>3.3E-3</v>
       </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="7"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>30225</v>
       </c>
@@ -1320,17 +958,11 @@
       <c r="D23" s="2">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="2">
         <v>-3.7100000000000001E-2</v>
       </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>30256</v>
       </c>
@@ -1343,17 +975,11 @@
       <c r="D24" s="2">
         <v>4.7800000000000002E-2</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="2">
         <v>-1.9900000000000001E-2</v>
       </c>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="7"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>30286</v>
       </c>
@@ -1366,17 +992,11 @@
       <c r="D25" s="2">
         <v>-2.0999999999999999E-3</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>30317</v>
       </c>
@@ -1389,17 +1009,11 @@
       <c r="D26" s="2">
         <v>2.69E-2</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="2">
         <v>-8.6E-3</v>
       </c>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>30348</v>
       </c>
@@ -1412,17 +1026,11 @@
       <c r="D27" s="2">
         <v>3.2400000000000005E-2</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="2">
         <v>6.5000000000000006E-3</v>
       </c>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>30376</v>
       </c>
@@ -1435,17 +1043,11 @@
       <c r="D28" s="2">
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="2">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>30407</v>
       </c>
@@ -1458,17 +1060,11 @@
       <c r="D29" s="2">
         <v>5.5000000000000005E-3</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="2">
         <v>5.5000000000000005E-3</v>
       </c>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>30437</v>
       </c>
@@ -1481,17 +1077,11 @@
       <c r="D30" s="2">
         <v>6.1600000000000002E-2</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="2">
         <v>-1.4199999999999999E-2</v>
       </c>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>30468</v>
       </c>
@@ -1504,17 +1094,11 @@
       <c r="D31" s="2">
         <v>9.1000000000000004E-3</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="2">
         <v>-3.85E-2</v>
       </c>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>30498</v>
       </c>
@@ -1527,17 +1111,11 @@
       <c r="D32" s="2">
         <v>1.46E-2</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="2">
         <v>5.6100000000000004E-2</v>
       </c>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>30529</v>
       </c>
@@ -1550,17 +1128,11 @@
       <c r="D33" s="2">
         <v>-4.2900000000000001E-2</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="2">
         <v>5.5300000000000002E-2</v>
       </c>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="7"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>30560</v>
       </c>
@@ -1573,17 +1145,11 @@
       <c r="D34" s="2">
         <v>5.6000000000000008E-3</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="2">
         <v>1.1000000000000001E-2</v>
       </c>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="7"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30590</v>
       </c>
@@ -1596,17 +1162,11 @@
       <c r="D35" s="2">
         <v>-3.6000000000000004E-2</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="2">
         <v>5.0599999999999999E-2</v>
       </c>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="7"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>30621</v>
       </c>
@@ -1619,17 +1179,11 @@
       <c r="D36" s="2">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="2">
         <v>-6.0999999999999995E-3</v>
       </c>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="7"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>30651</v>
       </c>
@@ -1642,17 +1196,11 @@
       <c r="D37" s="2">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="E37" s="33">
+      <c r="E37" s="2">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="7"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>30682</v>
       </c>
@@ -1665,17 +1213,11 @@
       <c r="D38" s="2">
         <v>-4.1999999999999997E-3</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="2">
         <v>7.6200000000000004E-2</v>
       </c>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="7"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>30713</v>
       </c>
@@ -1688,17 +1230,11 @@
       <c r="D39" s="2">
         <v>-1.7000000000000001E-2</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="2">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="7"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>30742</v>
       </c>
@@ -1711,17 +1247,11 @@
       <c r="D40" s="2">
         <v>7.000000000000001E-4</v>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="2">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="7"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>30773</v>
       </c>
@@ -1734,17 +1264,11 @@
       <c r="D41" s="2">
         <v>-1.2E-2</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="2">
         <v>1.29E-2</v>
       </c>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="7"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>30803</v>
       </c>
@@ -1757,17 +1281,11 @@
       <c r="D42" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="2">
         <v>2.3E-3</v>
       </c>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="7"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>30834</v>
       </c>
@@ -1780,17 +1298,11 @@
       <c r="D43" s="2">
         <v>-3.2000000000000002E-3</v>
       </c>
-      <c r="E43" s="33">
+      <c r="E43" s="2">
         <v>-2.6000000000000002E-2</v>
       </c>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="7"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>30864</v>
       </c>
@@ -1803,17 +1315,11 @@
       <c r="D44" s="2">
         <v>-2.2099999999999998E-2</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="2">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="7"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>30895</v>
       </c>
@@ -1826,17 +1332,11 @@
       <c r="D45" s="2">
         <v>-2.5999999999999999E-3</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="2">
         <v>-1.8200000000000001E-2</v>
       </c>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="7"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>30926</v>
       </c>
@@ -1849,17 +1349,11 @@
       <c r="D46" s="2">
         <v>2E-3</v>
       </c>
-      <c r="E46" s="33">
+      <c r="E46" s="2">
         <v>5.3099999999999994E-2</v>
       </c>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="7"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>30956</v>
       </c>
@@ -1872,17 +1366,11 @@
       <c r="D47" s="2">
         <v>-1.2E-2</v>
       </c>
-      <c r="E47" s="33">
+      <c r="E47" s="2">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="7"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>30987</v>
       </c>
@@ -1895,17 +1383,11 @@
       <c r="D48" s="2">
         <v>-6.1999999999999998E-3</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="2">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="7"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>31017</v>
       </c>
@@ -1918,17 +1400,11 @@
       <c r="D49" s="2">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="E49" s="33">
+      <c r="E49" s="2">
         <v>-1.8E-3</v>
       </c>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="7"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>31048</v>
       </c>
@@ -1941,17 +1417,11 @@
       <c r="D50" s="2">
         <v>3.2799999999999996E-2</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="2">
         <v>-5.4100000000000002E-2</v>
       </c>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>31079</v>
       </c>
@@ -1964,17 +1434,11 @@
       <c r="D51" s="2">
         <v>7.6E-3</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="2">
         <v>-1.2999999999999999E-3</v>
       </c>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="7"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>31107</v>
       </c>
@@ -1987,17 +1451,11 @@
       <c r="D52" s="2">
         <v>-1.15E-2</v>
       </c>
-      <c r="E52" s="33">
+      <c r="E52" s="2">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="7"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>31138</v>
       </c>
@@ -2010,17 +1468,11 @@
       <c r="D53" s="2">
         <v>1.4000000000000002E-3</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="2">
         <v>3.7200000000000004E-2</v>
       </c>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="7"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>31168</v>
       </c>
@@ -2033,17 +1485,11 @@
       <c r="D54" s="2">
         <v>-2.2499999999999999E-2</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="2">
         <v>-8.8000000000000005E-3</v>
       </c>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="7"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>31199</v>
       </c>
@@ -2056,17 +1502,11 @@
       <c r="D55" s="2">
         <v>5.6000000000000008E-3</v>
       </c>
-      <c r="E55" s="33">
+      <c r="E55" s="2">
         <v>5.5000000000000005E-3</v>
       </c>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="7"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>31229</v>
       </c>
@@ -2079,17 +1519,11 @@
       <c r="D56" s="2">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="2">
         <v>-1.6299999999999999E-2</v>
       </c>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="7"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>31260</v>
       </c>
@@ -2102,17 +1536,11 @@
       <c r="D57" s="2">
         <v>-3.4000000000000002E-3</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="2">
         <v>2.2799999999999997E-2</v>
       </c>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="7"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>31291</v>
       </c>
@@ -2125,17 +1553,11 @@
       <c r="D58" s="2">
         <v>-1.5800000000000002E-2</v>
       </c>
-      <c r="E58" s="33">
+      <c r="E58" s="2">
         <v>1.32E-2</v>
       </c>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="7"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>31321</v>
       </c>
@@ -2148,17 +1570,11 @@
       <c r="D59" s="2">
         <v>-1.5700000000000002E-2</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="2">
         <v>7.8000000000000005E-3</v>
       </c>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="7"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>31352</v>
       </c>
@@ -2171,17 +1587,11 @@
       <c r="D60" s="2">
         <v>2.3E-3</v>
       </c>
-      <c r="E60" s="33">
+      <c r="E60" s="2">
         <v>-2.87E-2</v>
       </c>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="7"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>31382</v>
       </c>
@@ -2194,17 +1604,11 @@
       <c r="D61" s="2">
         <v>-4.8999999999999998E-3</v>
       </c>
-      <c r="E61" s="33">
+      <c r="E61" s="2">
         <v>-1.5300000000000001E-2</v>
       </c>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="7"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>31413</v>
       </c>
@@ -2217,17 +1621,11 @@
       <c r="D62" s="2">
         <v>1.2199999999999999E-2</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="2">
         <v>5.3E-3</v>
       </c>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="7"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>31444</v>
       </c>
@@ -2240,17 +1638,11 @@
       <c r="D63" s="2">
         <v>-6.5000000000000006E-3</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="2">
         <v>-9.3999999999999986E-3</v>
       </c>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="7"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>31472</v>
       </c>
@@ -2263,17 +1655,11 @@
       <c r="D64" s="2">
         <v>-5.1999999999999998E-3</v>
       </c>
-      <c r="E64" s="33">
+      <c r="E64" s="2">
         <v>-4.4000000000000003E-3</v>
       </c>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="7"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>31503</v>
       </c>
@@ -2286,17 +1672,11 @@
       <c r="D65" s="2">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="2">
         <v>-2.8500000000000001E-2</v>
       </c>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="7"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>31533</v>
       </c>
@@ -2309,17 +1689,11 @@
       <c r="D66" s="2">
         <v>-1.32E-2</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="2">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="7"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>31564</v>
       </c>
@@ -2332,17 +1706,11 @@
       <c r="D67" s="2">
         <v>-9.1000000000000004E-3</v>
       </c>
-      <c r="E67" s="33">
+      <c r="E67" s="2">
         <v>1.3999999999999999E-2</v>
       </c>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="7"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>31594</v>
       </c>
@@ -2355,17 +1723,11 @@
       <c r="D68" s="2">
         <v>-3.3799999999999997E-2</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="2">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="7"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>31625</v>
       </c>
@@ -2378,17 +1740,11 @@
       <c r="D69" s="2">
         <v>-4.1799999999999997E-2</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="2">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="7"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>31656</v>
       </c>
@@ -2401,17 +1757,11 @@
       <c r="D70" s="2">
         <v>2.2799999999999997E-2</v>
       </c>
-      <c r="E70" s="33">
+      <c r="E70" s="2">
         <v>3.1800000000000002E-2</v>
       </c>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="7"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>31686</v>
       </c>
@@ -2424,17 +1774,11 @@
       <c r="D71" s="2">
         <v>-2.4900000000000002E-2</v>
       </c>
-      <c r="E71" s="33">
+      <c r="E71" s="2">
         <v>-1.3300000000000001E-2</v>
       </c>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="7"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>31717</v>
       </c>
@@ -2447,17 +1791,11 @@
       <c r="D72" s="2">
         <v>-1.9099999999999999E-2</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="2">
         <v>-7.000000000000001E-4</v>
       </c>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="7"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>31747</v>
       </c>
@@ -2470,17 +1808,11 @@
       <c r="D73" s="2">
         <v>7.000000000000001E-4</v>
       </c>
-      <c r="E73" s="33">
+      <c r="E73" s="2">
         <v>3.3E-3</v>
       </c>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="7"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>31778</v>
       </c>
@@ -2493,17 +1825,11 @@
       <c r="D74" s="2">
         <v>-1.8100000000000002E-2</v>
       </c>
-      <c r="E74" s="33">
+      <c r="E74" s="2">
         <v>-3.1600000000000003E-2</v>
       </c>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="7"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>31809</v>
       </c>
@@ -2516,17 +1842,11 @@
       <c r="D75" s="2">
         <v>3.49E-2</v>
       </c>
-      <c r="E75" s="33">
+      <c r="E75" s="2">
         <v>-0.06</v>
       </c>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="7"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>31837</v>
       </c>
@@ -2539,17 +1859,11 @@
       <c r="D76" s="2">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="E76" s="33">
+      <c r="E76" s="2">
         <v>1.6399999999999998E-2</v>
       </c>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="7"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>31868</v>
       </c>
@@ -2562,17 +1876,11 @@
       <c r="D77" s="2">
         <v>-1.7000000000000001E-2</v>
       </c>
-      <c r="E77" s="33">
+      <c r="E77" s="2">
         <v>-3.2000000000000002E-3</v>
       </c>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="7"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>31898</v>
       </c>
@@ -2585,17 +1893,11 @@
       <c r="D78" s="2">
         <v>-5.1999999999999998E-3</v>
       </c>
-      <c r="E78" s="33">
+      <c r="E78" s="2">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="7"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>31929</v>
       </c>
@@ -2608,17 +1910,11 @@
       <c r="D79" s="2">
         <v>-2.1899999999999999E-2</v>
       </c>
-      <c r="E79" s="33">
+      <c r="E79" s="2">
         <v>1.0700000000000001E-2</v>
       </c>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="7"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>31959</v>
       </c>
@@ -2631,17 +1927,11 @@
       <c r="D80" s="2">
         <v>-6.4000000000000003E-3</v>
       </c>
-      <c r="E80" s="33">
+      <c r="E80" s="2">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="7"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>31990</v>
       </c>
@@ -2654,17 +1944,11 @@
       <c r="D81" s="2">
         <v>-7.4000000000000003E-3</v>
       </c>
-      <c r="E81" s="33">
+      <c r="E81" s="2">
         <v>-9.4999999999999998E-3</v>
       </c>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="7"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>32021</v>
       </c>
@@ -2677,17 +1961,11 @@
       <c r="D82" s="2">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="E82" s="33">
+      <c r="E82" s="2">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="7"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>32051</v>
       </c>
@@ -2700,17 +1978,11 @@
       <c r="D83" s="2">
         <v>-8.4199999999999997E-2</v>
       </c>
-      <c r="E83" s="33">
+      <c r="E83" s="2">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="7"/>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>32082</v>
       </c>
@@ -2723,17 +1995,11 @@
       <c r="D84" s="2">
         <v>2.76E-2</v>
       </c>
-      <c r="E84" s="33">
+      <c r="E84" s="2">
         <v>3.0899999999999997E-2</v>
       </c>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="7"/>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>32112</v>
       </c>
@@ -2746,17 +2012,11 @@
       <c r="D85" s="2">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="E85" s="33">
+      <c r="E85" s="2">
         <v>-4.4600000000000001E-2</v>
       </c>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="7"/>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>32143</v>
       </c>
@@ -2769,17 +2029,11 @@
       <c r="D86" s="2">
         <v>-6.9999999999999993E-3</v>
       </c>
-      <c r="E86" s="33">
+      <c r="E86" s="2">
         <v>5.16E-2</v>
       </c>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="7"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>32174</v>
       </c>
@@ -2792,17 +2046,11 @@
       <c r="D87" s="2">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="E87" s="33">
+      <c r="E87" s="2">
         <v>-1.6399999999999998E-2</v>
       </c>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="7"/>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>32203</v>
       </c>
@@ -2815,17 +2063,11 @@
       <c r="D88" s="2">
         <v>6.1500000000000006E-2</v>
       </c>
-      <c r="E88" s="33">
+      <c r="E88" s="2">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="7"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>32234</v>
       </c>
@@ -2838,17 +2080,11 @@
       <c r="D89" s="2">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="E89" s="33">
+      <c r="E89" s="2">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="F89" s="32"/>
-      <c r="G89" s="32"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="7"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>32264</v>
       </c>
@@ -2861,17 +2097,11 @@
       <c r="D90" s="2">
         <v>-2.6499999999999999E-2</v>
       </c>
-      <c r="E90" s="33">
+      <c r="E90" s="2">
         <v>2.2799999999999997E-2</v>
       </c>
-      <c r="F90" s="32"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="7"/>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>32295</v>
       </c>
@@ -2884,17 +2114,11 @@
       <c r="D91" s="2">
         <v>2.12E-2</v>
       </c>
-      <c r="E91" s="33">
+      <c r="E91" s="2">
         <v>-1.1000000000000001E-2</v>
       </c>
-      <c r="F91" s="32"/>
-      <c r="G91" s="32"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="7"/>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>32325</v>
       </c>
@@ -2907,17 +2131,11 @@
       <c r="D92" s="2">
         <v>-2.0999999999999999E-3</v>
       </c>
-      <c r="E92" s="33">
+      <c r="E92" s="2">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="F92" s="32"/>
-      <c r="G92" s="32"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="7"/>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>32356</v>
       </c>
@@ -2930,17 +2148,11 @@
       <c r="D93" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="E93" s="33">
+      <c r="E93" s="2">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="F93" s="32"/>
-      <c r="G93" s="32"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="7"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>32387</v>
       </c>
@@ -2953,17 +2165,11 @@
       <c r="D94" s="2">
         <v>-1.2500000000000001E-2</v>
       </c>
-      <c r="E94" s="33">
+      <c r="E94" s="2">
         <v>-6.8000000000000005E-3</v>
       </c>
-      <c r="F94" s="32"/>
-      <c r="G94" s="32"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="7"/>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>32417</v>
       </c>
@@ -2976,17 +2182,11 @@
       <c r="D95" s="2">
         <v>-2.8999999999999998E-2</v>
       </c>
-      <c r="E95" s="33">
+      <c r="E95" s="2">
         <v>1.7100000000000001E-2</v>
       </c>
-      <c r="F95" s="32"/>
-      <c r="G95" s="32"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="7"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>32448</v>
       </c>
@@ -2999,17 +2199,11 @@
       <c r="D96" s="2">
         <v>-1.7399999999999999E-2</v>
       </c>
-      <c r="E96" s="33">
+      <c r="E96" s="2">
         <v>1.24E-2</v>
       </c>
-      <c r="F96" s="32"/>
-      <c r="G96" s="32"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="7"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>32478</v>
       </c>
@@ -3022,17 +2216,11 @@
       <c r="D97" s="2">
         <v>1.95E-2</v>
       </c>
-      <c r="E97" s="33">
+      <c r="E97" s="2">
         <v>-1.5600000000000001E-2</v>
       </c>
-      <c r="F97" s="32"/>
-      <c r="G97" s="32"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="7"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>32509</v>
       </c>
@@ -3045,17 +2233,11 @@
       <c r="D98" s="2">
         <v>-2.1400000000000002E-2</v>
       </c>
-      <c r="E98" s="33">
+      <c r="E98" s="2">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="F98" s="32"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="7"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>32540</v>
       </c>
@@ -3068,17 +2250,11 @@
       <c r="D99" s="2">
         <v>2.76E-2</v>
       </c>
-      <c r="E99" s="33">
+      <c r="E99" s="2">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="7"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>32568</v>
       </c>
@@ -3091,17 +2267,11 @@
       <c r="D100" s="2">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="E100" s="33">
+      <c r="E100" s="2">
         <v>4.6999999999999993E-3</v>
       </c>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="7"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>32599</v>
       </c>
@@ -3114,17 +2284,11 @@
       <c r="D101" s="2">
         <v>-5.7999999999999996E-3</v>
       </c>
-      <c r="E101" s="33">
+      <c r="E101" s="2">
         <v>-1.46E-2</v>
       </c>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="7"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>32629</v>
       </c>
@@ -3137,17 +2301,11 @@
       <c r="D102" s="2">
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="E102" s="33">
+      <c r="E102" s="2">
         <v>-8.3000000000000001E-3</v>
       </c>
-      <c r="F102" s="32"/>
-      <c r="G102" s="32"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="7"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>32660</v>
       </c>
@@ -3160,17 +2318,11 @@
       <c r="D103" s="2">
         <v>-1.0200000000000001E-2</v>
       </c>
-      <c r="E103" s="33">
+      <c r="E103" s="2">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="F103" s="32"/>
-      <c r="G103" s="32"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="7"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>32690</v>
       </c>
@@ -3183,17 +2335,11 @@
       <c r="D104" s="2">
         <v>-4.0199999999999993E-2</v>
       </c>
-      <c r="E104" s="33">
+      <c r="E104" s="2">
         <v>-2.8300000000000002E-2</v>
       </c>
-      <c r="F104" s="32"/>
-      <c r="G104" s="32"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="7"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>32721</v>
       </c>
@@ -3206,17 +2352,11 @@
       <c r="D105" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E105" s="33">
+      <c r="E105" s="2">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="F105" s="32"/>
-      <c r="G105" s="32"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="7"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>32752</v>
       </c>
@@ -3229,17 +2369,11 @@
       <c r="D106" s="2">
         <v>2.8000000000000004E-3</v>
       </c>
-      <c r="E106" s="33">
+      <c r="E106" s="2">
         <v>-1.34E-2</v>
       </c>
-      <c r="F106" s="32"/>
-      <c r="G106" s="32"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="7"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>32782</v>
       </c>
@@ -3252,17 +2386,11 @@
       <c r="D107" s="2">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="E107" s="33">
+      <c r="E107" s="2">
         <v>-1.03E-2</v>
       </c>
-      <c r="F107" s="32"/>
-      <c r="G107" s="32"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="7"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>32813</v>
       </c>
@@ -3275,17 +2403,11 @@
       <c r="D108" s="2">
         <v>-1.24E-2</v>
       </c>
-      <c r="E108" s="33">
+      <c r="E108" s="2">
         <v>-1.1200000000000002E-2</v>
       </c>
-      <c r="F108" s="32"/>
-      <c r="G108" s="32"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="7"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>32843</v>
       </c>
@@ -3298,17 +2420,11 @@
       <c r="D109" s="2">
         <v>-2.41E-2</v>
       </c>
-      <c r="E109" s="33">
+      <c r="E109" s="2">
         <v>2.8000000000000004E-3</v>
       </c>
-      <c r="F109" s="32"/>
-      <c r="G109" s="32"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="7"/>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>32874</v>
       </c>
@@ -3321,17 +2437,11 @@
       <c r="D110" s="2">
         <v>-1.29E-2</v>
       </c>
-      <c r="E110" s="33">
+      <c r="E110" s="2">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="F110" s="32"/>
-      <c r="G110" s="32"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="7"/>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>32905</v>
       </c>
@@ -3344,17 +2454,11 @@
       <c r="D111" s="2">
         <v>1.03E-2</v>
       </c>
-      <c r="E111" s="33">
+      <c r="E111" s="2">
         <v>6.0999999999999995E-3</v>
       </c>
-      <c r="F111" s="32"/>
-      <c r="G111" s="32"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="7"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>32933</v>
       </c>
@@ -3367,17 +2471,11 @@
       <c r="D112" s="2">
         <v>1.52E-2</v>
       </c>
-      <c r="E112" s="33">
+      <c r="E112" s="2">
         <v>-2.8999999999999998E-2</v>
       </c>
-      <c r="F112" s="32"/>
-      <c r="G112" s="32"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="7"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>32964</v>
       </c>
@@ -3390,17 +2488,11 @@
       <c r="D113" s="2">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E113" s="33">
+      <c r="E113" s="2">
         <v>-2.5499999999999998E-2</v>
       </c>
-      <c r="F113" s="32"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="7"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>32994</v>
       </c>
@@ -3413,17 +2505,11 @@
       <c r="D114" s="2">
         <v>-2.5699999999999997E-2</v>
       </c>
-      <c r="E114" s="33">
+      <c r="E114" s="2">
         <v>-3.7400000000000003E-2</v>
       </c>
-      <c r="F114" s="32"/>
-      <c r="G114" s="32"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="7"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>33025</v>
       </c>
@@ -3436,17 +2522,11 @@
       <c r="D115" s="2">
         <v>1.43E-2</v>
       </c>
-      <c r="E115" s="33">
+      <c r="E115" s="2">
         <v>-1.9400000000000001E-2</v>
       </c>
-      <c r="F115" s="32"/>
-      <c r="G115" s="32"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="7"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>33055</v>
       </c>
@@ -3459,17 +2539,11 @@
       <c r="D116" s="2">
         <v>-3.2099999999999997E-2</v>
       </c>
-      <c r="E116" s="33">
+      <c r="E116" s="2">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="F116" s="32"/>
-      <c r="G116" s="32"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="7"/>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>33086</v>
       </c>
@@ -3482,17 +2556,11 @@
       <c r="D117" s="2">
         <v>-3.5799999999999998E-2</v>
       </c>
-      <c r="E117" s="33">
+      <c r="E117" s="2">
         <v>1.5900000000000001E-2</v>
       </c>
-      <c r="F117" s="32"/>
-      <c r="G117" s="32"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="7"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>33117</v>
       </c>
@@ -3505,17 +2573,11 @@
       <c r="D118" s="2">
         <v>-3.6699999999999997E-2</v>
       </c>
-      <c r="E118" s="33">
+      <c r="E118" s="2">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="F118" s="32"/>
-      <c r="G118" s="32"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="7"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>33147</v>
       </c>
@@ -3528,17 +2590,11 @@
       <c r="D119" s="2">
         <v>-5.5199999999999999E-2</v>
       </c>
-      <c r="E119" s="33">
+      <c r="E119" s="2">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F119" s="32"/>
-      <c r="G119" s="32"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="7"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>33178</v>
       </c>
@@ -3551,17 +2607,11 @@
       <c r="D120" s="2">
         <v>3.3E-3</v>
       </c>
-      <c r="E120" s="33">
+      <c r="E120" s="2">
         <v>-3.1600000000000003E-2</v>
       </c>
-      <c r="F120" s="32"/>
-      <c r="G120" s="32"/>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="7"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>33208</v>
       </c>
@@ -3574,17 +2624,11 @@
       <c r="D121" s="2">
         <v>8.1000000000000013E-3</v>
       </c>
-      <c r="E121" s="33">
+      <c r="E121" s="2">
         <v>-1.5600000000000001E-2</v>
       </c>
-      <c r="F121" s="32"/>
-      <c r="G121" s="32"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="7"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>33239</v>
       </c>
@@ -3597,17 +2641,11 @@
       <c r="D122" s="2">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E122" s="33">
+      <c r="E122" s="2">
         <v>-1.8500000000000003E-2</v>
       </c>
-      <c r="F122" s="32"/>
-      <c r="G122" s="32"/>
-      <c r="H122" s="2"/>
-      <c r="I122" s="2"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="7"/>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>33270</v>
       </c>
@@ -3620,17 +2658,11 @@
       <c r="D123" s="2">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="E123" s="33">
+      <c r="E123" s="2">
         <v>-5.3E-3</v>
       </c>
-      <c r="F123" s="32"/>
-      <c r="G123" s="32"/>
-      <c r="H123" s="2"/>
-      <c r="I123" s="2"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="7"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>33298</v>
       </c>
@@ -3643,17 +2675,11 @@
       <c r="D124" s="2">
         <v>3.9E-2</v>
       </c>
-      <c r="E124" s="33">
+      <c r="E124" s="2">
         <v>-1.24E-2</v>
       </c>
-      <c r="F124" s="32"/>
-      <c r="G124" s="32"/>
-      <c r="H124" s="2"/>
-      <c r="I124" s="2"/>
-      <c r="J124" s="6"/>
-      <c r="K124" s="7"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>33329</v>
       </c>
@@ -3666,17 +2692,11 @@
       <c r="D125" s="2">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="E125" s="33">
+      <c r="E125" s="2">
         <v>1.41E-2</v>
       </c>
-      <c r="F125" s="32"/>
-      <c r="G125" s="32"/>
-      <c r="H125" s="2"/>
-      <c r="I125" s="2"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="7"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>33359</v>
       </c>
@@ -3689,17 +2709,11 @@
       <c r="D126" s="2">
         <v>-3.4000000000000002E-3</v>
       </c>
-      <c r="E126" s="33">
+      <c r="E126" s="2">
         <v>-5.6999999999999993E-3</v>
       </c>
-      <c r="F126" s="32"/>
-      <c r="G126" s="32"/>
-      <c r="H126" s="2"/>
-      <c r="I126" s="2"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="7"/>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>33390</v>
       </c>
@@ -3712,17 +2726,11 @@
       <c r="D127" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="E127" s="33">
+      <c r="E127" s="2">
         <v>1.2199999999999999E-2</v>
       </c>
-      <c r="F127" s="32"/>
-      <c r="G127" s="32"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="7"/>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>33420</v>
       </c>
@@ -3735,17 +2743,11 @@
       <c r="D128" s="2">
         <v>-9.300000000000001E-3</v>
       </c>
-      <c r="E128" s="33">
+      <c r="E128" s="2">
         <v>-1.26E-2</v>
       </c>
-      <c r="F128" s="32"/>
-      <c r="G128" s="32"/>
-      <c r="H128" s="2"/>
-      <c r="I128" s="2"/>
-      <c r="J128" s="6"/>
-      <c r="K128" s="7"/>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>33451</v>
       </c>
@@ -3758,17 +2760,11 @@
       <c r="D129" s="2">
         <v>1.6E-2</v>
       </c>
-      <c r="E129" s="33">
+      <c r="E129" s="2">
         <v>-7.9000000000000008E-3</v>
       </c>
-      <c r="F129" s="32"/>
-      <c r="G129" s="32"/>
-      <c r="H129" s="2"/>
-      <c r="I129" s="2"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="7"/>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>33482</v>
       </c>
@@ -3781,17 +2777,11 @@
       <c r="D130" s="2">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="E130" s="33">
+      <c r="E130" s="2">
         <v>-0.01</v>
       </c>
-      <c r="F130" s="32"/>
-      <c r="G130" s="32"/>
-      <c r="H130" s="2"/>
-      <c r="I130" s="2"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="7"/>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>33512</v>
       </c>
@@ -3804,17 +2794,11 @@
       <c r="D131" s="2">
         <v>9.0000000000000011E-3</v>
       </c>
-      <c r="E131" s="33">
+      <c r="E131" s="2">
         <v>-4.4000000000000003E-3</v>
       </c>
-      <c r="F131" s="32"/>
-      <c r="G131" s="32"/>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="7"/>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>33543</v>
       </c>
@@ -3827,17 +2811,11 @@
       <c r="D132" s="2">
         <v>-4.7999999999999996E-3</v>
       </c>
-      <c r="E132" s="33">
+      <c r="E132" s="2">
         <v>-1.9299999999999998E-2</v>
       </c>
-      <c r="F132" s="32"/>
-      <c r="G132" s="32"/>
-      <c r="H132" s="2"/>
-      <c r="I132" s="2"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="7"/>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>33573</v>
       </c>
@@ -3850,17 +2828,11 @@
       <c r="D133" s="2">
         <v>-2.23E-2</v>
       </c>
-      <c r="E133" s="33">
+      <c r="E133" s="2">
         <v>-4.0399999999999998E-2</v>
       </c>
-      <c r="F133" s="32"/>
-      <c r="G133" s="32"/>
-      <c r="H133" s="2"/>
-      <c r="I133" s="2"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="7"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>33604</v>
       </c>
@@ -3873,17 +2845,11 @@
       <c r="D134" s="2">
         <v>8.4499999999999992E-2</v>
       </c>
-      <c r="E134" s="33">
+      <c r="E134" s="2">
         <v>4.53E-2</v>
       </c>
-      <c r="F134" s="32"/>
-      <c r="G134" s="32"/>
-      <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="7"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>33635</v>
       </c>
@@ -3896,17 +2862,11 @@
       <c r="D135" s="2">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="E135" s="33">
+      <c r="E135" s="2">
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="F135" s="32"/>
-      <c r="G135" s="32"/>
-      <c r="H135" s="2"/>
-      <c r="I135" s="2"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="7"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>33664</v>
       </c>
@@ -3919,17 +2879,11 @@
       <c r="D136" s="2">
         <v>-1.04E-2</v>
       </c>
-      <c r="E136" s="33">
+      <c r="E136" s="2">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="F136" s="32"/>
-      <c r="G136" s="32"/>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="7"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>33695</v>
       </c>
@@ -3942,17 +2896,11 @@
       <c r="D137" s="2">
         <v>-6.1100000000000002E-2</v>
       </c>
-      <c r="E137" s="33">
+      <c r="E137" s="2">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F137" s="32"/>
-      <c r="G137" s="32"/>
-      <c r="H137" s="2"/>
-      <c r="I137" s="2"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="7"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>33725</v>
       </c>
@@ -3965,17 +2913,11 @@
       <c r="D138" s="2">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E138" s="33">
+      <c r="E138" s="2">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="F138" s="32"/>
-      <c r="G138" s="32"/>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="7"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>33756</v>
       </c>
@@ -3988,17 +2930,11 @@
       <c r="D139" s="2">
         <v>-3.0899999999999997E-2</v>
       </c>
-      <c r="E139" s="33">
+      <c r="E139" s="2">
         <v>3.4099999999999998E-2</v>
       </c>
-      <c r="F139" s="32"/>
-      <c r="G139" s="32"/>
-      <c r="H139" s="2"/>
-      <c r="I139" s="2"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="7"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>33786</v>
       </c>
@@ -4011,17 +2947,11 @@
       <c r="D140" s="2">
         <v>-4.4000000000000003E-3</v>
       </c>
-      <c r="E140" s="33">
+      <c r="E140" s="2">
         <v>-5.3E-3</v>
       </c>
-      <c r="F140" s="32"/>
-      <c r="G140" s="32"/>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="7"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>33817</v>
       </c>
@@ -4034,17 +2964,11 @@
       <c r="D141" s="2">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="E141" s="33">
+      <c r="E141" s="2">
         <v>-1.04E-2</v>
       </c>
-      <c r="F141" s="32"/>
-      <c r="G141" s="32"/>
-      <c r="H141" s="2"/>
-      <c r="I141" s="2"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="7"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>33848</v>
       </c>
@@ -4057,17 +2981,11 @@
       <c r="D142" s="2">
         <v>5.6000000000000008E-3</v>
       </c>
-      <c r="E142" s="33">
+      <c r="E142" s="2">
         <v>-2.0999999999999999E-3</v>
       </c>
-      <c r="F142" s="32"/>
-      <c r="G142" s="32"/>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="7"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>33878</v>
       </c>
@@ -4080,17 +2998,11 @@
       <c r="D143" s="2">
         <v>2.0499999999999997E-2</v>
       </c>
-      <c r="E143" s="33">
+      <c r="E143" s="2">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="F143" s="32"/>
-      <c r="G143" s="32"/>
-      <c r="H143" s="2"/>
-      <c r="I143" s="2"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="7"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>33909</v>
       </c>
@@ -4103,17 +3015,11 @@
       <c r="D144" s="2">
         <v>3.7000000000000005E-2</v>
       </c>
-      <c r="E144" s="33">
+      <c r="E144" s="2">
         <v>-1.4800000000000001E-2</v>
       </c>
-      <c r="F144" s="32"/>
-      <c r="G144" s="32"/>
-      <c r="H144" s="2"/>
-      <c r="I144" s="2"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="7"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>33939</v>
       </c>
@@ -4126,17 +3032,11 @@
       <c r="D145" s="2">
         <v>1.6399999999999998E-2</v>
       </c>
-      <c r="E145" s="33">
+      <c r="E145" s="2">
         <v>2.52E-2</v>
       </c>
-      <c r="F145" s="32"/>
-      <c r="G145" s="32"/>
-      <c r="H145" s="2"/>
-      <c r="I145" s="2"/>
-      <c r="J145" s="6"/>
-      <c r="K145" s="7"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>33970</v>
       </c>
@@ -4149,17 +3049,11 @@
       <c r="D146" s="2">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="E146" s="33">
+      <c r="E146" s="2">
         <v>5.8700000000000002E-2</v>
       </c>
-      <c r="F146" s="32"/>
-      <c r="G146" s="32"/>
-      <c r="H146" s="2"/>
-      <c r="I146" s="2"/>
-      <c r="J146" s="6"/>
-      <c r="K146" s="7"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>34001</v>
       </c>
@@ -4172,17 +3066,11 @@
       <c r="D147" s="2">
         <v>-3.4300000000000004E-2</v>
       </c>
-      <c r="E147" s="33">
+      <c r="E147" s="2">
         <v>6.4199999999999993E-2</v>
       </c>
-      <c r="F147" s="32"/>
-      <c r="G147" s="32"/>
-      <c r="H147" s="2"/>
-      <c r="I147" s="2"/>
-      <c r="J147" s="6"/>
-      <c r="K147" s="7"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>34029</v>
       </c>
@@ -4195,17 +3083,11 @@
       <c r="D148" s="2">
         <v>2.3E-3</v>
       </c>
-      <c r="E148" s="33">
+      <c r="E148" s="2">
         <v>1.2199999999999999E-2</v>
       </c>
-      <c r="F148" s="32"/>
-      <c r="G148" s="32"/>
-      <c r="H148" s="2"/>
-      <c r="I148" s="2"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="7"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>34060</v>
       </c>
@@ -4218,17 +3100,11 @@
       <c r="D149" s="2">
         <v>-6.9999999999999993E-3</v>
       </c>
-      <c r="E149" s="33">
+      <c r="E149" s="2">
         <v>2.6099999999999998E-2</v>
       </c>
-      <c r="F149" s="32"/>
-      <c r="G149" s="32"/>
-      <c r="H149" s="2"/>
-      <c r="I149" s="2"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="7"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>34090</v>
       </c>
@@ -4241,17 +3117,11 @@
       <c r="D150" s="2">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="E150" s="33">
+      <c r="E150" s="2">
         <v>-3.4099999999999998E-2</v>
       </c>
-      <c r="F150" s="32"/>
-      <c r="G150" s="32"/>
-      <c r="H150" s="2"/>
-      <c r="I150" s="2"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="7"/>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>34121</v>
       </c>
@@ -4264,17 +3134,11 @@
       <c r="D151" s="2">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="E151" s="33">
+      <c r="E151" s="2">
         <v>2.6099999999999998E-2</v>
       </c>
-      <c r="F151" s="32"/>
-      <c r="G151" s="32"/>
-      <c r="H151" s="2"/>
-      <c r="I151" s="2"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="7"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>34151</v>
       </c>
@@ -4287,17 +3151,11 @@
       <c r="D152" s="2">
         <v>9.300000000000001E-3</v>
       </c>
-      <c r="E152" s="33">
+      <c r="E152" s="2">
         <v>3.2400000000000005E-2</v>
       </c>
-      <c r="F152" s="32"/>
-      <c r="G152" s="32"/>
-      <c r="H152" s="2"/>
-      <c r="I152" s="2"/>
-      <c r="J152" s="6"/>
-      <c r="K152" s="7"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>34182</v>
       </c>
@@ -4310,17 +3168,11 @@
       <c r="D153" s="2">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="E153" s="33">
+      <c r="E153" s="2">
         <v>-4.5000000000000005E-3</v>
       </c>
-      <c r="F153" s="32"/>
-      <c r="G153" s="32"/>
-      <c r="H153" s="2"/>
-      <c r="I153" s="2"/>
-      <c r="J153" s="6"/>
-      <c r="K153" s="7"/>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>34213</v>
       </c>
@@ -4333,17 +3185,11 @@
       <c r="D154" s="2">
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="E154" s="33">
+      <c r="E154" s="2">
         <v>-4.5000000000000005E-3</v>
       </c>
-      <c r="F154" s="32"/>
-      <c r="G154" s="32"/>
-      <c r="H154" s="2"/>
-      <c r="I154" s="2"/>
-      <c r="J154" s="6"/>
-      <c r="K154" s="7"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>34243</v>
       </c>
@@ -4356,17 +3202,11 @@
       <c r="D155" s="2">
         <v>1.4499999999999999E-2</v>
       </c>
-      <c r="E155" s="33">
+      <c r="E155" s="2">
         <v>-1.54E-2</v>
       </c>
-      <c r="F155" s="32"/>
-      <c r="G155" s="32"/>
-      <c r="H155" s="2"/>
-      <c r="I155" s="2"/>
-      <c r="J155" s="6"/>
-      <c r="K155" s="7"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>34274</v>
       </c>
@@ -4379,17 +3219,11 @@
       <c r="D156" s="2">
         <v>-1.43E-2</v>
       </c>
-      <c r="E156" s="33">
+      <c r="E156" s="2">
         <v>-2.7000000000000001E-3</v>
       </c>
-      <c r="F156" s="32"/>
-      <c r="G156" s="32"/>
-      <c r="H156" s="2"/>
-      <c r="I156" s="2"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="7"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>34304</v>
       </c>
@@ -4402,17 +3236,11 @@
       <c r="D157" s="2">
         <v>1.2199999999999999E-2</v>
       </c>
-      <c r="E157" s="33">
+      <c r="E157" s="2">
         <v>5.6999999999999993E-3</v>
       </c>
-      <c r="F157" s="32"/>
-      <c r="G157" s="32"/>
-      <c r="H157" s="2"/>
-      <c r="I157" s="2"/>
-      <c r="J157" s="6"/>
-      <c r="K157" s="7"/>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>34335</v>
       </c>
@@ -4425,17 +3253,11 @@
       <c r="D158" s="2">
         <v>1.4000000000000002E-3</v>
       </c>
-      <c r="E158" s="33">
+      <c r="E158" s="2">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="F158" s="32"/>
-      <c r="G158" s="32"/>
-      <c r="H158" s="2"/>
-      <c r="I158" s="2"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="7"/>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>34366</v>
       </c>
@@ -4448,17 +3270,11 @@
       <c r="D159" s="2">
         <v>2.7300000000000001E-2</v>
       </c>
-      <c r="E159" s="33">
+      <c r="E159" s="2">
         <v>-1.44E-2</v>
       </c>
-      <c r="F159" s="32"/>
-      <c r="G159" s="32"/>
-      <c r="H159" s="2"/>
-      <c r="I159" s="2"/>
-      <c r="J159" s="6"/>
-      <c r="K159" s="7"/>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>34394</v>
       </c>
@@ -4471,17 +3287,11 @@
       <c r="D160" s="2">
         <v>-9.7999999999999997E-3</v>
       </c>
-      <c r="E160" s="33">
+      <c r="E160" s="2">
         <v>1.3100000000000001E-2</v>
       </c>
-      <c r="F160" s="32"/>
-      <c r="G160" s="32"/>
-      <c r="H160" s="2"/>
-      <c r="I160" s="2"/>
-      <c r="J160" s="6"/>
-      <c r="K160" s="7"/>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>34425</v>
       </c>
@@ -4494,17 +3304,11 @@
       <c r="D161" s="2">
         <v>-9.300000000000001E-3</v>
       </c>
-      <c r="E161" s="33">
+      <c r="E161" s="2">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="F161" s="32"/>
-      <c r="G161" s="32"/>
-      <c r="H161" s="2"/>
-      <c r="I161" s="2"/>
-      <c r="J161" s="6"/>
-      <c r="K161" s="7"/>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
         <v>34455</v>
       </c>
@@ -4517,17 +3321,11 @@
       <c r="D162" s="2">
         <v>-2.0199999999999999E-2</v>
       </c>
-      <c r="E162" s="33">
+      <c r="E162" s="2">
         <v>2E-3</v>
       </c>
-      <c r="F162" s="32"/>
-      <c r="G162" s="32"/>
-      <c r="H162" s="2"/>
-      <c r="I162" s="2"/>
-      <c r="J162" s="6"/>
-      <c r="K162" s="7"/>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
         <v>34486</v>
       </c>
@@ -4540,17 +3338,11 @@
       <c r="D163" s="2">
         <v>-4.6999999999999993E-3</v>
       </c>
-      <c r="E163" s="33">
+      <c r="E163" s="2">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="F163" s="32"/>
-      <c r="G163" s="32"/>
-      <c r="H163" s="2"/>
-      <c r="I163" s="2"/>
-      <c r="J163" s="6"/>
-      <c r="K163" s="7"/>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>34516</v>
       </c>
@@ -4563,17 +3355,11 @@
       <c r="D164" s="2">
         <v>-1.72E-2</v>
       </c>
-      <c r="E164" s="33">
+      <c r="E164" s="2">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F164" s="32"/>
-      <c r="G164" s="32"/>
-      <c r="H164" s="2"/>
-      <c r="I164" s="2"/>
-      <c r="J164" s="6"/>
-      <c r="K164" s="7"/>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>34547</v>
       </c>
@@ -4586,17 +3372,11 @@
       <c r="D165" s="2">
         <v>1.3300000000000001E-2</v>
       </c>
-      <c r="E165" s="33">
+      <c r="E165" s="2">
         <v>-2.8300000000000002E-2</v>
       </c>
-      <c r="F165" s="32"/>
-      <c r="G165" s="32"/>
-      <c r="H165" s="2"/>
-      <c r="I165" s="2"/>
-      <c r="J165" s="6"/>
-      <c r="K165" s="7"/>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>34578</v>
       </c>
@@ -4609,17 +3389,11 @@
       <c r="D166" s="2">
         <v>2.8199999999999999E-2</v>
       </c>
-      <c r="E166" s="33">
+      <c r="E166" s="2">
         <v>-1.9099999999999999E-2</v>
       </c>
-      <c r="F166" s="32"/>
-      <c r="G166" s="32"/>
-      <c r="H166" s="2"/>
-      <c r="I166" s="2"/>
-      <c r="J166" s="6"/>
-      <c r="K166" s="7"/>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>34608</v>
       </c>
@@ -4632,17 +3406,11 @@
       <c r="D167" s="2">
         <v>-2.3599999999999999E-2</v>
       </c>
-      <c r="E167" s="33">
+      <c r="E167" s="2">
         <v>-1.7500000000000002E-2</v>
       </c>
-      <c r="F167" s="32"/>
-      <c r="G167" s="32"/>
-      <c r="H167" s="2"/>
-      <c r="I167" s="2"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="7"/>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
         <v>34639</v>
       </c>
@@ -4655,17 +3423,11 @@
       <c r="D168" s="2">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="E168" s="33">
+      <c r="E168" s="2">
         <v>-9.4999999999999998E-3</v>
       </c>
-      <c r="F168" s="32"/>
-      <c r="G168" s="32"/>
-      <c r="H168" s="2"/>
-      <c r="I168" s="2"/>
-      <c r="J168" s="6"/>
-      <c r="K168" s="7"/>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>34669</v>
       </c>
@@ -4678,17 +3440,11 @@
       <c r="D169" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="E169" s="33">
+      <c r="E169" s="2">
         <v>5.3E-3</v>
       </c>
-      <c r="F169" s="32"/>
-      <c r="G169" s="32"/>
-      <c r="H169" s="2"/>
-      <c r="I169" s="2"/>
-      <c r="J169" s="6"/>
-      <c r="K169" s="7"/>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>34700</v>
       </c>
@@ -4701,17 +3457,11 @@
       <c r="D170" s="2">
         <v>-2.6499999999999999E-2</v>
       </c>
-      <c r="E170" s="33">
+      <c r="E170" s="2">
         <v>8.199999999999999E-3</v>
       </c>
-      <c r="F170" s="32"/>
-      <c r="G170" s="32"/>
-      <c r="H170" s="2"/>
-      <c r="I170" s="2"/>
-      <c r="J170" s="6"/>
-      <c r="K170" s="7"/>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>34731</v>
       </c>
@@ -4724,17 +3474,11 @@
       <c r="D171" s="2">
         <v>-6.8999999999999999E-3</v>
       </c>
-      <c r="E171" s="33">
+      <c r="E171" s="2">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="F171" s="32"/>
-      <c r="G171" s="32"/>
-      <c r="H171" s="2"/>
-      <c r="I171" s="2"/>
-      <c r="J171" s="6"/>
-      <c r="K171" s="7"/>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>34759</v>
       </c>
@@ -4747,17 +3491,11 @@
       <c r="D172" s="2">
         <v>-6.9999999999999993E-3</v>
       </c>
-      <c r="E172" s="33">
+      <c r="E172" s="2">
         <v>-1.0700000000000001E-2</v>
       </c>
-      <c r="F172" s="32"/>
-      <c r="G172" s="32"/>
-      <c r="H172" s="2"/>
-      <c r="I172" s="2"/>
-      <c r="J172" s="6"/>
-      <c r="K172" s="7"/>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>34790</v>
       </c>
@@ -4770,17 +3508,11 @@
       <c r="D173" s="2">
         <v>-6.3E-3</v>
       </c>
-      <c r="E173" s="33">
+      <c r="E173" s="2">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="F173" s="32"/>
-      <c r="G173" s="32"/>
-      <c r="H173" s="2"/>
-      <c r="I173" s="2"/>
-      <c r="J173" s="6"/>
-      <c r="K173" s="7"/>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="5">
         <v>34820</v>
       </c>
@@ -4793,17 +3525,11 @@
       <c r="D174" s="2">
         <v>-2.2000000000000002E-2</v>
       </c>
-      <c r="E174" s="33">
+      <c r="E174" s="2">
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="F174" s="32"/>
-      <c r="G174" s="32"/>
-      <c r="H174" s="2"/>
-      <c r="I174" s="2"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="7"/>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="5">
         <v>34851</v>
       </c>
@@ -4816,17 +3542,11 @@
       <c r="D175" s="2">
         <v>2.9300000000000003E-2</v>
       </c>
-      <c r="E175" s="33">
+      <c r="E175" s="2">
         <v>-2.2700000000000001E-2</v>
       </c>
-      <c r="F175" s="32"/>
-      <c r="G175" s="32"/>
-      <c r="H175" s="2"/>
-      <c r="I175" s="2"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="7"/>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="5">
         <v>34881</v>
       </c>
@@ -4839,17 +3559,11 @@
       <c r="D176" s="2">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="E176" s="33">
+      <c r="E176" s="2">
         <v>-1.6899999999999998E-2</v>
       </c>
-      <c r="F176" s="32"/>
-      <c r="G176" s="32"/>
-      <c r="H176" s="2"/>
-      <c r="I176" s="2"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="7"/>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="5">
         <v>34912</v>
       </c>
@@ -4862,17 +3576,11 @@
       <c r="D177" s="2">
         <v>1.6E-2</v>
       </c>
-      <c r="E177" s="33">
+      <c r="E177" s="2">
         <v>2.7099999999999999E-2</v>
       </c>
-      <c r="F177" s="32"/>
-      <c r="G177" s="32"/>
-      <c r="H177" s="2"/>
-      <c r="I177" s="2"/>
-      <c r="J177" s="6"/>
-      <c r="K177" s="7"/>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="5">
         <v>34943</v>
       </c>
@@ -4885,17 +3593,11 @@
       <c r="D178" s="2">
         <v>-2.1099999999999997E-2</v>
       </c>
-      <c r="E178" s="33">
+      <c r="E178" s="2">
         <v>-7.7000000000000002E-3</v>
       </c>
-      <c r="F178" s="32"/>
-      <c r="G178" s="32"/>
-      <c r="H178" s="2"/>
-      <c r="I178" s="2"/>
-      <c r="J178" s="6"/>
-      <c r="K178" s="7"/>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>34973</v>
       </c>
@@ -4908,17 +3610,11 @@
       <c r="D179" s="2">
         <v>-3.7400000000000003E-2</v>
       </c>
-      <c r="E179" s="33">
+      <c r="E179" s="2">
         <v>-7.4999999999999997E-3</v>
       </c>
-      <c r="F179" s="32"/>
-      <c r="G179" s="32"/>
-      <c r="H179" s="2"/>
-      <c r="I179" s="2"/>
-      <c r="J179" s="6"/>
-      <c r="K179" s="7"/>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="5">
         <v>35004</v>
       </c>
@@ -4931,17 +3627,11 @@
       <c r="D180" s="2">
         <v>-1.1599999999999999E-2</v>
       </c>
-      <c r="E180" s="33">
+      <c r="E180" s="2">
         <v>9.3999999999999986E-3</v>
       </c>
-      <c r="F180" s="32"/>
-      <c r="G180" s="32"/>
-      <c r="H180" s="2"/>
-      <c r="I180" s="2"/>
-      <c r="J180" s="6"/>
-      <c r="K180" s="7"/>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="5">
         <v>35034</v>
       </c>
@@ -4954,17 +3644,11 @@
       <c r="D181" s="2">
         <v>5.6999999999999993E-3</v>
       </c>
-      <c r="E181" s="33">
+      <c r="E181" s="2">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="F181" s="32"/>
-      <c r="G181" s="32"/>
-      <c r="H181" s="2"/>
-      <c r="I181" s="2"/>
-      <c r="J181" s="6"/>
-      <c r="K181" s="7"/>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="5">
         <v>35065</v>
       </c>
@@ -4977,17 +3661,11 @@
       <c r="D182" s="2">
         <v>-2.6099999999999998E-2</v>
       </c>
-      <c r="E182" s="33">
+      <c r="E182" s="2">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="F182" s="32"/>
-      <c r="G182" s="32"/>
-      <c r="H182" s="2"/>
-      <c r="I182" s="2"/>
-      <c r="J182" s="6"/>
-      <c r="K182" s="7"/>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>35096</v>
       </c>
@@ -5000,17 +3678,11 @@
       <c r="D183" s="2">
         <v>1.8700000000000001E-2</v>
       </c>
-      <c r="E183" s="33">
+      <c r="E183" s="2">
         <v>-1.43E-2</v>
       </c>
-      <c r="F183" s="32"/>
-      <c r="G183" s="32"/>
-      <c r="H183" s="2"/>
-      <c r="I183" s="2"/>
-      <c r="J183" s="6"/>
-      <c r="K183" s="7"/>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="5">
         <v>35125</v>
       </c>
@@ -5023,17 +3695,11 @@
       <c r="D184" s="2">
         <v>1.3000000000000001E-2</v>
       </c>
-      <c r="E184" s="33">
+      <c r="E184" s="2">
         <v>9.8999999999999991E-3</v>
       </c>
-      <c r="F184" s="32"/>
-      <c r="G184" s="32"/>
-      <c r="H184" s="2"/>
-      <c r="I184" s="2"/>
-      <c r="J184" s="6"/>
-      <c r="K184" s="7"/>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="5">
         <v>35156</v>
       </c>
@@ -5046,17 +3712,11 @@
       <c r="D185" s="2">
         <v>4.9100000000000005E-2</v>
       </c>
-      <c r="E185" s="33">
+      <c r="E185" s="2">
         <v>-3.9E-2</v>
       </c>
-      <c r="F185" s="32"/>
-      <c r="G185" s="32"/>
-      <c r="H185" s="2"/>
-      <c r="I185" s="2"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="7"/>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="5">
         <v>35186</v>
       </c>
@@ -5069,17 +3729,11 @@
       <c r="D186" s="2">
         <v>3.0299999999999997E-2</v>
       </c>
-      <c r="E186" s="33">
+      <c r="E186" s="2">
         <v>-1.21E-2</v>
       </c>
-      <c r="F186" s="32"/>
-      <c r="G186" s="32"/>
-      <c r="H186" s="2"/>
-      <c r="I186" s="2"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="7"/>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="5">
         <v>35217</v>
       </c>
@@ -5092,17 +3746,11 @@
       <c r="D187" s="2">
         <v>-3.5799999999999998E-2</v>
       </c>
-      <c r="E187" s="33">
+      <c r="E187" s="2">
         <v>1.55E-2</v>
       </c>
-      <c r="F187" s="32"/>
-      <c r="G187" s="32"/>
-      <c r="H187" s="2"/>
-      <c r="I187" s="2"/>
-      <c r="J187" s="6"/>
-      <c r="K187" s="7"/>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="5">
         <v>35247</v>
       </c>
@@ -5115,17 +3763,11 @@
       <c r="D188" s="2">
         <v>-3.8300000000000001E-2</v>
       </c>
-      <c r="E188" s="33">
+      <c r="E188" s="2">
         <v>4.4199999999999996E-2</v>
       </c>
-      <c r="F188" s="32"/>
-      <c r="G188" s="32"/>
-      <c r="H188" s="2"/>
-      <c r="I188" s="2"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="7"/>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>35278</v>
       </c>
@@ -5138,17 +3780,11 @@
       <c r="D189" s="2">
         <v>2.29E-2</v>
       </c>
-      <c r="E189" s="33">
+      <c r="E189" s="2">
         <v>-4.3E-3</v>
       </c>
-      <c r="F189" s="32"/>
-      <c r="G189" s="32"/>
-      <c r="H189" s="2"/>
-      <c r="I189" s="2"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="7"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>35309</v>
       </c>
@@ -5161,17 +3797,11 @@
       <c r="D190" s="2">
         <v>-8.6999999999999994E-3</v>
       </c>
-      <c r="E190" s="33">
+      <c r="E190" s="2">
         <v>-3.1200000000000002E-2</v>
       </c>
-      <c r="F190" s="32"/>
-      <c r="G190" s="32"/>
-      <c r="H190" s="2"/>
-      <c r="I190" s="2"/>
-      <c r="J190" s="6"/>
-      <c r="K190" s="7"/>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>35339</v>
       </c>
@@ -5184,17 +3814,11 @@
       <c r="D191" s="2">
         <v>-4.4699999999999997E-2</v>
       </c>
-      <c r="E191" s="33">
+      <c r="E191" s="2">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="F191" s="32"/>
-      <c r="G191" s="32"/>
-      <c r="H191" s="2"/>
-      <c r="I191" s="2"/>
-      <c r="J191" s="6"/>
-      <c r="K191" s="7"/>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="5">
         <v>35370</v>
       </c>
@@ -5207,17 +3831,11 @@
       <c r="D192" s="2">
         <v>-3.9100000000000003E-2</v>
       </c>
-      <c r="E192" s="33">
+      <c r="E192" s="2">
         <v>1.21E-2</v>
       </c>
-      <c r="F192" s="32"/>
-      <c r="G192" s="32"/>
-      <c r="H192" s="2"/>
-      <c r="I192" s="2"/>
-      <c r="J192" s="6"/>
-      <c r="K192" s="7"/>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="5">
         <v>35400</v>
       </c>
@@ -5230,17 +3848,11 @@
       <c r="D193" s="2">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="E193" s="33">
+      <c r="E193" s="2">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="F193" s="32"/>
-      <c r="G193" s="32"/>
-      <c r="H193" s="2"/>
-      <c r="I193" s="2"/>
-      <c r="J193" s="6"/>
-      <c r="K193" s="7"/>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="5">
         <v>35431</v>
       </c>
@@ -5253,17 +3865,11 @@
       <c r="D194" s="2">
         <v>-1.84E-2</v>
       </c>
-      <c r="E194" s="33">
+      <c r="E194" s="2">
         <v>-1.6500000000000001E-2</v>
       </c>
-      <c r="F194" s="32"/>
-      <c r="G194" s="32"/>
-      <c r="H194" s="2"/>
-      <c r="I194" s="2"/>
-      <c r="J194" s="6"/>
-      <c r="K194" s="7"/>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="5">
         <v>35462</v>
       </c>
@@ -5276,17 +3882,11 @@
       <c r="D195" s="2">
         <v>-2.9100000000000001E-2</v>
       </c>
-      <c r="E195" s="33">
+      <c r="E195" s="2">
         <v>5.1900000000000002E-2</v>
       </c>
-      <c r="F195" s="32"/>
-      <c r="G195" s="32"/>
-      <c r="H195" s="2"/>
-      <c r="I195" s="2"/>
-      <c r="J195" s="6"/>
-      <c r="K195" s="7"/>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="5">
         <v>35490</v>
       </c>
@@ -5299,17 +3899,11 @@
       <c r="D196" s="2">
         <v>-3.8E-3</v>
       </c>
-      <c r="E196" s="33">
+      <c r="E196" s="2">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="F196" s="32"/>
-      <c r="G196" s="32"/>
-      <c r="H196" s="2"/>
-      <c r="I196" s="2"/>
-      <c r="J196" s="6"/>
-      <c r="K196" s="7"/>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="5">
         <v>35521</v>
       </c>
@@ -5322,17 +3916,11 @@
       <c r="D197" s="2">
         <v>-5.6500000000000002E-2</v>
       </c>
-      <c r="E197" s="33">
+      <c r="E197" s="2">
         <v>-7.000000000000001E-4</v>
       </c>
-      <c r="F197" s="32"/>
-      <c r="G197" s="32"/>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="7"/>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="5">
         <v>35551</v>
       </c>
@@ -5345,17 +3933,11 @@
       <c r="D198" s="2">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="E198" s="33">
+      <c r="E198" s="2">
         <v>-3.9100000000000003E-2</v>
       </c>
-      <c r="F198" s="32"/>
-      <c r="G198" s="32"/>
-      <c r="H198" s="2"/>
-      <c r="I198" s="2"/>
-      <c r="J198" s="6"/>
-      <c r="K198" s="7"/>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="5">
         <v>35582</v>
       </c>
@@ -5368,17 +3950,11 @@
       <c r="D199" s="2">
         <v>1.34E-2</v>
       </c>
-      <c r="E199" s="33">
+      <c r="E199" s="2">
         <v>1.21E-2</v>
       </c>
-      <c r="F199" s="32"/>
-      <c r="G199" s="32"/>
-      <c r="H199" s="2"/>
-      <c r="I199" s="2"/>
-      <c r="J199" s="6"/>
-      <c r="K199" s="7"/>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="5">
         <v>35612</v>
       </c>
@@ -5391,17 +3967,11 @@
       <c r="D200" s="2">
         <v>-2.7999999999999997E-2</v>
       </c>
-      <c r="E200" s="33">
+      <c r="E200" s="2">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="F200" s="32"/>
-      <c r="G200" s="32"/>
-      <c r="H200" s="2"/>
-      <c r="I200" s="2"/>
-      <c r="J200" s="6"/>
-      <c r="K200" s="7"/>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="5">
         <v>35643</v>
       </c>
@@ -5414,17 +3984,11 @@
       <c r="D201" s="2">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="E201" s="33">
+      <c r="E201" s="2">
         <v>1.37E-2</v>
       </c>
-      <c r="F201" s="32"/>
-      <c r="G201" s="32"/>
-      <c r="H201" s="2"/>
-      <c r="I201" s="2"/>
-      <c r="J201" s="6"/>
-      <c r="K201" s="7"/>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="5">
         <v>35674</v>
       </c>
@@ -5437,17 +4001,11 @@
       <c r="D202" s="2">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="E202" s="33">
+      <c r="E202" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="F202" s="32"/>
-      <c r="G202" s="32"/>
-      <c r="H202" s="2"/>
-      <c r="I202" s="2"/>
-      <c r="J202" s="6"/>
-      <c r="K202" s="7"/>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="5">
         <v>35704</v>
       </c>
@@ -5460,17 +4018,11 @@
       <c r="D203" s="2">
         <v>-6.8000000000000005E-3</v>
       </c>
-      <c r="E203" s="33">
+      <c r="E203" s="2">
         <v>1.9699999999999999E-2</v>
       </c>
-      <c r="F203" s="32"/>
-      <c r="G203" s="32"/>
-      <c r="H203" s="2"/>
-      <c r="I203" s="2"/>
-      <c r="J203" s="6"/>
-      <c r="K203" s="7"/>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="5">
         <v>35735</v>
       </c>
@@ -5483,17 +4035,11 @@
       <c r="D204" s="2">
         <v>-4.9699999999999994E-2</v>
       </c>
-      <c r="E204" s="33">
+      <c r="E204" s="2">
         <v>8.199999999999999E-3</v>
       </c>
-      <c r="F204" s="32"/>
-      <c r="G204" s="32"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
-      <c r="J204" s="6"/>
-      <c r="K204" s="7"/>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="5">
         <v>35765</v>
       </c>
@@ -5506,17 +4052,11 @@
       <c r="D205" s="2">
         <v>-2.3599999999999999E-2</v>
       </c>
-      <c r="E205" s="33">
+      <c r="E205" s="2">
         <v>3.5099999999999999E-2</v>
       </c>
-      <c r="F205" s="32"/>
-      <c r="G205" s="32"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="6"/>
-      <c r="K205" s="7"/>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>35796</v>
       </c>
@@ -5529,17 +4069,11 @@
       <c r="D206" s="2">
         <v>-1.15E-2</v>
       </c>
-      <c r="E206" s="33">
+      <c r="E206" s="2">
         <v>-1.4499999999999999E-2</v>
       </c>
-      <c r="F206" s="32"/>
-      <c r="G206" s="32"/>
-      <c r="H206" s="2"/>
-      <c r="I206" s="2"/>
-      <c r="J206" s="6"/>
-      <c r="K206" s="7"/>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>35827</v>
       </c>
@@ -5552,17 +4086,11 @@
       <c r="D207" s="2">
         <v>-1E-4</v>
       </c>
-      <c r="E207" s="33">
+      <c r="E207" s="2">
         <v>-1.1999999999999999E-3</v>
       </c>
-      <c r="F207" s="32"/>
-      <c r="G207" s="32"/>
-      <c r="H207" s="2"/>
-      <c r="I207" s="2"/>
-      <c r="J207" s="6"/>
-      <c r="K207" s="7"/>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>35855</v>
       </c>
@@ -5575,17 +4103,11 @@
       <c r="D208" s="2">
         <v>-9.300000000000001E-3</v>
       </c>
-      <c r="E208" s="33">
+      <c r="E208" s="2">
         <v>1.04E-2</v>
       </c>
-      <c r="F208" s="32"/>
-      <c r="G208" s="32"/>
-      <c r="H208" s="2"/>
-      <c r="I208" s="2"/>
-      <c r="J208" s="6"/>
-      <c r="K208" s="7"/>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>35886</v>
       </c>
@@ -5598,17 +4120,11 @@
       <c r="D209" s="2">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="E209" s="33">
+      <c r="E209" s="2">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="F209" s="32"/>
-      <c r="G209" s="32"/>
-      <c r="H209" s="2"/>
-      <c r="I209" s="2"/>
-      <c r="J209" s="6"/>
-      <c r="K209" s="7"/>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="5">
         <v>35916</v>
       </c>
@@ -5621,17 +4137,11 @@
       <c r="D210" s="2">
         <v>-3.7599999999999995E-2</v>
       </c>
-      <c r="E210" s="33">
+      <c r="E210" s="2">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="F210" s="32"/>
-      <c r="G210" s="32"/>
-      <c r="H210" s="2"/>
-      <c r="I210" s="2"/>
-      <c r="J210" s="6"/>
-      <c r="K210" s="7"/>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="5">
         <v>35947</v>
       </c>
@@ -5644,17 +4154,11 @@
       <c r="D211" s="2">
         <v>-3.1600000000000003E-2</v>
       </c>
-      <c r="E211" s="33">
+      <c r="E211" s="2">
         <v>-2.3E-2</v>
       </c>
-      <c r="F211" s="32"/>
-      <c r="G211" s="32"/>
-      <c r="H211" s="2"/>
-      <c r="I211" s="2"/>
-      <c r="J211" s="6"/>
-      <c r="K211" s="7"/>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="5">
         <v>35977</v>
       </c>
@@ -5667,17 +4171,11 @@
       <c r="D212" s="2">
         <v>-5.1200000000000002E-2</v>
       </c>
-      <c r="E212" s="33">
+      <c r="E212" s="2">
         <v>-9.7000000000000003E-3</v>
       </c>
-      <c r="F212" s="32"/>
-      <c r="G212" s="32"/>
-      <c r="H212" s="2"/>
-      <c r="I212" s="2"/>
-      <c r="J212" s="6"/>
-      <c r="K212" s="7"/>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="5">
         <v>36008</v>
       </c>
@@ -5690,17 +4188,11 @@
       <c r="D213" s="2">
         <v>-5.2999999999999999E-2</v>
       </c>
-      <c r="E213" s="33">
+      <c r="E213" s="2">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F213" s="32"/>
-      <c r="G213" s="32"/>
-      <c r="H213" s="2"/>
-      <c r="I213" s="2"/>
-      <c r="J213" s="6"/>
-      <c r="K213" s="7"/>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="5">
         <v>36039</v>
       </c>
@@ -5713,17 +4205,11 @@
       <c r="D214" s="2">
         <v>-1.1999999999999999E-3</v>
       </c>
-      <c r="E214" s="33">
+      <c r="E214" s="2">
         <v>-3.3099999999999997E-2</v>
       </c>
-      <c r="F214" s="32"/>
-      <c r="G214" s="32"/>
-      <c r="H214" s="2"/>
-      <c r="I214" s="2"/>
-      <c r="J214" s="6"/>
-      <c r="K214" s="7"/>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="5">
         <v>36069</v>
       </c>
@@ -5736,17 +4222,11 @@
       <c r="D215" s="2">
         <v>-3.32E-2</v>
       </c>
-      <c r="E215" s="33">
+      <c r="E215" s="2">
         <v>-2.2000000000000002E-2</v>
       </c>
-      <c r="F215" s="32"/>
-      <c r="G215" s="32"/>
-      <c r="H215" s="2"/>
-      <c r="I215" s="2"/>
-      <c r="J215" s="6"/>
-      <c r="K215" s="7"/>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="5">
         <v>36100</v>
       </c>
@@ -5759,17 +4239,11 @@
       <c r="D216" s="2">
         <v>1.0700000000000001E-2</v>
       </c>
-      <c r="E216" s="33">
+      <c r="E216" s="2">
         <v>-3.1400000000000004E-2</v>
       </c>
-      <c r="F216" s="32"/>
-      <c r="G216" s="32"/>
-      <c r="H216" s="2"/>
-      <c r="I216" s="2"/>
-      <c r="J216" s="6"/>
-      <c r="K216" s="7"/>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="5">
         <v>36130</v>
       </c>
@@ -5782,17 +4256,11 @@
       <c r="D217" s="2">
         <v>-3.3E-3</v>
       </c>
-      <c r="E217" s="33">
+      <c r="E217" s="2">
         <v>-4.4600000000000001E-2</v>
       </c>
-      <c r="F217" s="32"/>
-      <c r="G217" s="32"/>
-      <c r="H217" s="2"/>
-      <c r="I217" s="2"/>
-      <c r="J217" s="6"/>
-      <c r="K217" s="7"/>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="5">
         <v>36161</v>
       </c>
@@ -5805,17 +4273,11 @@
       <c r="D218" s="2">
         <v>3.9000000000000003E-3</v>
       </c>
-      <c r="E218" s="33">
+      <c r="E218" s="2">
         <v>-4.0300000000000002E-2</v>
       </c>
-      <c r="F218" s="32"/>
-      <c r="G218" s="32"/>
-      <c r="H218" s="2"/>
-      <c r="I218" s="2"/>
-      <c r="J218" s="6"/>
-      <c r="K218" s="7"/>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="5">
         <v>36192</v>
       </c>
@@ -5828,17 +4290,11 @@
       <c r="D219" s="2">
         <v>-5.6799999999999996E-2</v>
       </c>
-      <c r="E219" s="33">
+      <c r="E219" s="2">
         <v>1.3999999999999999E-2</v>
       </c>
-      <c r="F219" s="32"/>
-      <c r="G219" s="32"/>
-      <c r="H219" s="2"/>
-      <c r="I219" s="2"/>
-      <c r="J219" s="6"/>
-      <c r="K219" s="7"/>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="5">
         <v>36220</v>
       </c>
@@ -5851,17 +4307,11 @@
       <c r="D220" s="2">
         <v>-3.9399999999999998E-2</v>
       </c>
-      <c r="E220" s="33">
+      <c r="E220" s="2">
         <v>-2.64E-2</v>
       </c>
-      <c r="F220" s="32"/>
-      <c r="G220" s="32"/>
-      <c r="H220" s="2"/>
-      <c r="I220" s="2"/>
-      <c r="J220" s="6"/>
-      <c r="K220" s="7"/>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="5">
         <v>36251</v>
       </c>
@@ -5874,17 +4324,11 @@
       <c r="D221" s="2">
         <v>3.9900000000000005E-2</v>
       </c>
-      <c r="E221" s="33">
+      <c r="E221" s="2">
         <v>2.5099999999999997E-2</v>
       </c>
-      <c r="F221" s="32"/>
-      <c r="G221" s="32"/>
-      <c r="H221" s="2"/>
-      <c r="I221" s="2"/>
-      <c r="J221" s="6"/>
-      <c r="K221" s="7"/>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="5">
         <v>36281</v>
       </c>
@@ -5897,17 +4341,11 @@
       <c r="D222" s="2">
         <v>3.4200000000000001E-2</v>
       </c>
-      <c r="E222" s="33">
+      <c r="E222" s="2">
         <v>2.4E-2</v>
       </c>
-      <c r="F222" s="32"/>
-      <c r="G222" s="32"/>
-      <c r="H222" s="2"/>
-      <c r="I222" s="2"/>
-      <c r="J222" s="6"/>
-      <c r="K222" s="7"/>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="5">
         <v>36312</v>
       </c>
@@ -5920,17 +4358,11 @@
       <c r="D223" s="2">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="E223" s="33">
+      <c r="E223" s="2">
         <v>-3.5900000000000001E-2</v>
       </c>
-      <c r="F223" s="32"/>
-      <c r="G223" s="32"/>
-      <c r="H223" s="2"/>
-      <c r="I223" s="2"/>
-      <c r="J223" s="6"/>
-      <c r="K223" s="7"/>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="5">
         <v>36342</v>
       </c>
@@ -5943,17 +4375,11 @@
       <c r="D224" s="2">
         <v>2.6699999999999998E-2</v>
       </c>
-      <c r="E224" s="33">
+      <c r="E224" s="2">
         <v>-7.7000000000000002E-3</v>
       </c>
-      <c r="F224" s="32"/>
-      <c r="G224" s="32"/>
-      <c r="H224" s="2"/>
-      <c r="I224" s="2"/>
-      <c r="J224" s="6"/>
-      <c r="K224" s="7"/>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="5">
         <v>36373</v>
       </c>
@@ -5966,17 +4392,11 @@
       <c r="D225" s="2">
         <v>-1.2800000000000001E-2</v>
       </c>
-      <c r="E225" s="33">
+      <c r="E225" s="2">
         <v>-1.3100000000000001E-2</v>
       </c>
-      <c r="F225" s="32"/>
-      <c r="G225" s="32"/>
-      <c r="H225" s="2"/>
-      <c r="I225" s="2"/>
-      <c r="J225" s="6"/>
-      <c r="K225" s="7"/>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>36404</v>
       </c>
@@ -5989,17 +4409,11 @@
       <c r="D226" s="2">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="E226" s="33">
+      <c r="E226" s="2">
         <v>-3.39E-2</v>
       </c>
-      <c r="F226" s="32"/>
-      <c r="G226" s="32"/>
-      <c r="H226" s="2"/>
-      <c r="I226" s="2"/>
-      <c r="J226" s="6"/>
-      <c r="K226" s="7"/>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="5">
         <v>36434</v>
       </c>
@@ -6012,17 +4426,11 @@
       <c r="D227" s="2">
         <v>-6.9500000000000006E-2</v>
       </c>
-      <c r="E227" s="33">
+      <c r="E227" s="2">
         <v>-2.8799999999999999E-2</v>
       </c>
-      <c r="F227" s="32"/>
-      <c r="G227" s="32"/>
-      <c r="H227" s="2"/>
-      <c r="I227" s="2"/>
-      <c r="J227" s="6"/>
-      <c r="K227" s="7"/>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="5">
         <v>36465</v>
       </c>
@@ -6035,17 +4443,11 @@
       <c r="D228" s="2">
         <v>7.3800000000000004E-2</v>
       </c>
-      <c r="E228" s="33">
+      <c r="E228" s="2">
         <v>-6.5000000000000002E-2</v>
       </c>
-      <c r="F228" s="32"/>
-      <c r="G228" s="32"/>
-      <c r="H228" s="2"/>
-      <c r="I228" s="2"/>
-      <c r="J228" s="6"/>
-      <c r="K228" s="7"/>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="5">
         <v>36495</v>
       </c>
@@ -6058,17 +4460,11 @@
       <c r="D229" s="2">
         <v>7.1500000000000008E-2</v>
       </c>
-      <c r="E229" s="33">
+      <c r="E229" s="2">
         <v>-8.6699999999999999E-2</v>
       </c>
-      <c r="F229" s="32"/>
-      <c r="G229" s="32"/>
-      <c r="H229" s="2"/>
-      <c r="I229" s="2"/>
-      <c r="J229" s="6"/>
-      <c r="K229" s="7"/>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="5">
         <v>36526</v>
       </c>
@@ -6081,17 +4477,11 @@
       <c r="D230" s="2">
         <v>4.9500000000000002E-2</v>
       </c>
-      <c r="E230" s="33">
+      <c r="E230" s="2">
         <v>-3.0999999999999999E-3</v>
       </c>
-      <c r="F230" s="32"/>
-      <c r="G230" s="32"/>
-      <c r="H230" s="2"/>
-      <c r="I230" s="2"/>
-      <c r="J230" s="6"/>
-      <c r="K230" s="7"/>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="5">
         <v>36557</v>
       </c>
@@ -6104,17 +4494,11 @@
       <c r="D231" s="2">
         <v>0.21710000000000002</v>
       </c>
-      <c r="E231" s="33">
+      <c r="E231" s="2">
         <v>-9.9399999999999988E-2</v>
       </c>
-      <c r="F231" s="32"/>
-      <c r="G231" s="32"/>
-      <c r="H231" s="2"/>
-      <c r="I231" s="2"/>
-      <c r="J231" s="6"/>
-      <c r="K231" s="7"/>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="5">
         <v>36586</v>
       </c>
@@ -6127,17 +4511,11 @@
       <c r="D232" s="2">
         <v>-0.16879999999999998</v>
       </c>
-      <c r="E232" s="33">
+      <c r="E232" s="2">
         <v>7.3700000000000002E-2</v>
       </c>
-      <c r="F232" s="32"/>
-      <c r="G232" s="32"/>
-      <c r="H232" s="2"/>
-      <c r="I232" s="2"/>
-      <c r="J232" s="6"/>
-      <c r="K232" s="7"/>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="5">
         <v>36617</v>
       </c>
@@ -6150,17 +4528,11 @@
       <c r="D233" s="2">
         <v>-7.7499999999999999E-2</v>
       </c>
-      <c r="E233" s="33">
+      <c r="E233" s="2">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="F233" s="32"/>
-      <c r="G233" s="32"/>
-      <c r="H233" s="2"/>
-      <c r="I233" s="2"/>
-      <c r="J233" s="6"/>
-      <c r="K233" s="7"/>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="5">
         <v>36647</v>
       </c>
@@ -6173,17 +4545,11 @@
       <c r="D234" s="2">
         <v>-5.1100000000000007E-2</v>
       </c>
-      <c r="E234" s="33">
+      <c r="E234" s="2">
         <v>2.5600000000000001E-2</v>
       </c>
-      <c r="F234" s="32"/>
-      <c r="G234" s="32"/>
-      <c r="H234" s="2"/>
-      <c r="I234" s="2"/>
-      <c r="J234" s="6"/>
-      <c r="K234" s="7"/>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="5">
         <v>36678</v>
       </c>
@@ -6196,17 +4562,11 @@
       <c r="D235" s="2">
         <v>0.1386</v>
       </c>
-      <c r="E235" s="33">
+      <c r="E235" s="2">
         <v>-9.8599999999999993E-2</v>
       </c>
-      <c r="F235" s="32"/>
-      <c r="G235" s="32"/>
-      <c r="H235" s="2"/>
-      <c r="I235" s="2"/>
-      <c r="J235" s="6"/>
-      <c r="K235" s="7"/>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="5">
         <v>36708</v>
       </c>
@@ -6219,17 +4579,11 @@
       <c r="D236" s="2">
         <v>-2.7900000000000001E-2</v>
       </c>
-      <c r="E236" s="33">
+      <c r="E236" s="2">
         <v>8.14E-2</v>
       </c>
-      <c r="F236" s="32"/>
-      <c r="G236" s="32"/>
-      <c r="H236" s="2"/>
-      <c r="I236" s="2"/>
-      <c r="J236" s="6"/>
-      <c r="K236" s="7"/>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="5">
         <v>36739</v>
       </c>
@@ -6242,17 +4596,11 @@
       <c r="D237" s="2">
         <v>-1.1299999999999999E-2</v>
       </c>
-      <c r="E237" s="33">
+      <c r="E237" s="2">
         <v>-6.8000000000000005E-3</v>
       </c>
-      <c r="F237" s="32"/>
-      <c r="G237" s="32"/>
-      <c r="H237" s="2"/>
-      <c r="I237" s="2"/>
-      <c r="J237" s="6"/>
-      <c r="K237" s="7"/>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="5">
         <v>36770</v>
       </c>
@@ -6265,17 +4613,11 @@
       <c r="D238" s="2">
         <v>-1.3899999999999999E-2</v>
       </c>
-      <c r="E238" s="33">
+      <c r="E238" s="2">
         <v>6.2400000000000004E-2</v>
       </c>
-      <c r="F238" s="32"/>
-      <c r="G238" s="32"/>
-      <c r="H238" s="2"/>
-      <c r="I238" s="2"/>
-      <c r="J238" s="6"/>
-      <c r="K238" s="7"/>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="5">
         <v>36800</v>
       </c>
@@ -6288,17 +4630,11 @@
       <c r="D239" s="2">
         <v>-3.7599999999999995E-2</v>
       </c>
-      <c r="E239" s="33">
+      <c r="E239" s="2">
         <v>5.5199999999999999E-2</v>
       </c>
-      <c r="F239" s="32"/>
-      <c r="G239" s="32"/>
-      <c r="H239" s="2"/>
-      <c r="I239" s="2"/>
-      <c r="J239" s="6"/>
-      <c r="K239" s="7"/>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="5">
         <v>36831</v>
       </c>
@@ -6311,17 +4647,11 @@
       <c r="D240" s="2">
         <v>-2.7900000000000001E-2</v>
       </c>
-      <c r="E240" s="33">
+      <c r="E240" s="2">
         <v>0.113</v>
       </c>
-      <c r="F240" s="32"/>
-      <c r="G240" s="32"/>
-      <c r="H240" s="2"/>
-      <c r="I240" s="2"/>
-      <c r="J240" s="6"/>
-      <c r="K240" s="7"/>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="5">
         <v>36861</v>
       </c>
@@ -6334,17 +4664,11 @@
       <c r="D241" s="2">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="E241" s="33">
+      <c r="E241" s="2">
         <v>7.3300000000000004E-2</v>
       </c>
-      <c r="F241" s="32"/>
-      <c r="G241" s="32"/>
-      <c r="H241" s="2"/>
-      <c r="I241" s="2"/>
-      <c r="J241" s="6"/>
-      <c r="K241" s="7"/>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="5">
         <v>36892</v>
       </c>
@@ -6357,17 +4681,11 @@
       <c r="D242" s="2">
         <v>6.5700000000000008E-2</v>
       </c>
-      <c r="E242" s="33">
+      <c r="E242" s="2">
         <v>-4.9000000000000002E-2</v>
       </c>
-      <c r="F242" s="32"/>
-      <c r="G242" s="32"/>
-      <c r="H242" s="2"/>
-      <c r="I242" s="2"/>
-      <c r="J242" s="6"/>
-      <c r="K242" s="7"/>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="5">
         <v>36923</v>
       </c>
@@ -6380,17 +4698,11 @@
       <c r="D243" s="2">
         <v>-7.4000000000000003E-3</v>
       </c>
-      <c r="E243" s="33">
+      <c r="E243" s="2">
         <v>0.129</v>
       </c>
-      <c r="F243" s="32"/>
-      <c r="G243" s="32"/>
-      <c r="H243" s="2"/>
-      <c r="I243" s="2"/>
-      <c r="J243" s="6"/>
-      <c r="K243" s="7"/>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="5">
         <v>36951</v>
       </c>
@@ -6403,17 +4715,11 @@
       <c r="D244" s="2">
         <v>3.4000000000000002E-3</v>
       </c>
-      <c r="E244" s="33">
+      <c r="E244" s="2">
         <v>6.4500000000000002E-2</v>
       </c>
-      <c r="F244" s="32"/>
-      <c r="G244" s="32"/>
-      <c r="H244" s="2"/>
-      <c r="I244" s="2"/>
-      <c r="J244" s="6"/>
-      <c r="K244" s="7"/>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="5">
         <v>36982</v>
       </c>
@@ -6426,17 +4732,11 @@
       <c r="D245" s="2">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="E245" s="33">
+      <c r="E245" s="2">
         <v>-4.6900000000000004E-2</v>
       </c>
-      <c r="F245" s="32"/>
-      <c r="G245" s="32"/>
-      <c r="H245" s="2"/>
-      <c r="I245" s="2"/>
-      <c r="J245" s="6"/>
-      <c r="K245" s="7"/>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="5">
         <v>37012</v>
       </c>
@@ -6449,17 +4749,11 @@
       <c r="D246" s="2">
         <v>2.6000000000000002E-2</v>
       </c>
-      <c r="E246" s="33">
+      <c r="E246" s="2">
         <v>3.1400000000000004E-2</v>
       </c>
-      <c r="F246" s="32"/>
-      <c r="G246" s="32"/>
-      <c r="H246" s="2"/>
-      <c r="I246" s="2"/>
-      <c r="J246" s="6"/>
-      <c r="K246" s="7"/>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" s="5">
         <v>37043</v>
       </c>
@@ -6472,17 +4766,11 @@
       <c r="D247" s="2">
         <v>6.0499999999999998E-2</v>
       </c>
-      <c r="E247" s="33">
+      <c r="E247" s="2">
         <v>-1.06E-2</v>
       </c>
-      <c r="F247" s="32"/>
-      <c r="G247" s="32"/>
-      <c r="H247" s="2"/>
-      <c r="I247" s="2"/>
-      <c r="J247" s="6"/>
-      <c r="K247" s="7"/>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="5">
         <v>37073</v>
       </c>
@@ -6495,17 +4783,11 @@
       <c r="D248" s="2">
         <v>-4.3499999999999997E-2</v>
       </c>
-      <c r="E248" s="33">
+      <c r="E248" s="2">
         <v>5.5800000000000002E-2</v>
       </c>
-      <c r="F248" s="32"/>
-      <c r="G248" s="32"/>
-      <c r="H248" s="2"/>
-      <c r="I248" s="2"/>
-      <c r="J248" s="6"/>
-      <c r="K248" s="7"/>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="5">
         <v>37104</v>
       </c>
@@ -6518,17 +4800,11 @@
       <c r="D249" s="2">
         <v>2.4900000000000002E-2</v>
       </c>
-      <c r="E249" s="33">
+      <c r="E249" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F249" s="32"/>
-      <c r="G249" s="32"/>
-      <c r="H249" s="2"/>
-      <c r="I249" s="2"/>
-      <c r="J249" s="6"/>
-      <c r="K249" s="7"/>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" s="5">
         <v>37135</v>
       </c>
@@ -6541,17 +4817,11 @@
       <c r="D250" s="2">
         <v>-6.13E-2</v>
       </c>
-      <c r="E250" s="33">
+      <c r="E250" s="2">
         <v>1.6E-2</v>
       </c>
-      <c r="F250" s="32"/>
-      <c r="G250" s="32"/>
-      <c r="H250" s="2"/>
-      <c r="I250" s="2"/>
-      <c r="J250" s="6"/>
-      <c r="K250" s="7"/>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="5">
         <v>37165</v>
       </c>
@@ -6564,17 +4834,11 @@
       <c r="D251" s="2">
         <v>7.6299999999999993E-2</v>
       </c>
-      <c r="E251" s="33">
+      <c r="E251" s="2">
         <v>-8.1099999999999992E-2</v>
       </c>
-      <c r="F251" s="32"/>
-      <c r="G251" s="32"/>
-      <c r="H251" s="2"/>
-      <c r="I251" s="2"/>
-      <c r="J251" s="6"/>
-      <c r="K251" s="7"/>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="5">
         <v>37196</v>
       </c>
@@ -6587,17 +4851,11 @@
       <c r="D252" s="2">
         <v>-4.0999999999999995E-3</v>
       </c>
-      <c r="E252" s="33">
+      <c r="E252" s="2">
         <v>0.02</v>
       </c>
-      <c r="F252" s="32"/>
-      <c r="G252" s="32"/>
-      <c r="H252" s="2"/>
-      <c r="I252" s="2"/>
-      <c r="J252" s="6"/>
-      <c r="K252" s="7"/>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="5">
         <v>37226</v>
       </c>
@@ -6610,17 +4868,11 @@
       <c r="D253" s="2">
         <v>4.5700000000000005E-2</v>
       </c>
-      <c r="E253" s="33">
+      <c r="E253" s="2">
         <v>1.1000000000000001E-2</v>
       </c>
-      <c r="F253" s="32"/>
-      <c r="G253" s="32"/>
-      <c r="H253" s="2"/>
-      <c r="I253" s="2"/>
-      <c r="J253" s="6"/>
-      <c r="K253" s="7"/>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="5">
         <v>37257</v>
       </c>
@@ -6633,17 +4885,11 @@
       <c r="D254" s="2">
         <v>1.1899999999999999E-2</v>
       </c>
-      <c r="E254" s="33">
+      <c r="E254" s="2">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="F254" s="32"/>
-      <c r="G254" s="32"/>
-      <c r="H254" s="2"/>
-      <c r="I254" s="2"/>
-      <c r="J254" s="6"/>
-      <c r="K254" s="7"/>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="5">
         <v>37288</v>
       </c>
@@ -6656,17 +4902,11 @@
       <c r="D255" s="2">
         <v>-1.1000000000000001E-2</v>
       </c>
-      <c r="E255" s="33">
+      <c r="E255" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F255" s="32"/>
-      <c r="G255" s="32"/>
-      <c r="H255" s="2"/>
-      <c r="I255" s="2"/>
-      <c r="J255" s="6"/>
-      <c r="K255" s="7"/>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="5">
         <v>37316</v>
       </c>
@@ -6679,17 +4919,11 @@
       <c r="D256" s="2">
         <v>4.2300000000000004E-2</v>
       </c>
-      <c r="E256" s="33">
+      <c r="E256" s="2">
         <v>1.1000000000000001E-2</v>
       </c>
-      <c r="F256" s="32"/>
-      <c r="G256" s="32"/>
-      <c r="H256" s="2"/>
-      <c r="I256" s="2"/>
-      <c r="J256" s="6"/>
-      <c r="K256" s="7"/>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="5">
         <v>37347</v>
       </c>
@@ -6702,17 +4936,11 @@
       <c r="D257" s="2">
         <v>5.9400000000000001E-2</v>
       </c>
-      <c r="E257" s="33">
+      <c r="E257" s="2">
         <v>3.9300000000000002E-2</v>
       </c>
-      <c r="F257" s="32"/>
-      <c r="G257" s="32"/>
-      <c r="H257" s="2"/>
-      <c r="I257" s="2"/>
-      <c r="J257" s="6"/>
-      <c r="K257" s="7"/>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" s="5">
         <v>37377</v>
       </c>
@@ -6725,17 +4953,11 @@
       <c r="D258" s="2">
         <v>-3.2099999999999997E-2</v>
       </c>
-      <c r="E258" s="33">
+      <c r="E258" s="2">
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="F258" s="32"/>
-      <c r="G258" s="32"/>
-      <c r="H258" s="2"/>
-      <c r="I258" s="2"/>
-      <c r="J258" s="6"/>
-      <c r="K258" s="7"/>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" s="5">
         <v>37408</v>
       </c>
@@ -6748,17 +4970,11 @@
       <c r="D259" s="2">
         <v>4.2599999999999999E-2</v>
       </c>
-      <c r="E259" s="33">
+      <c r="E259" s="2">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="F259" s="32"/>
-      <c r="G259" s="32"/>
-      <c r="H259" s="2"/>
-      <c r="I259" s="2"/>
-      <c r="J259" s="6"/>
-      <c r="K259" s="7"/>
-    </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" s="5">
         <v>37438</v>
       </c>
@@ -6771,17 +4987,11 @@
       <c r="D260" s="2">
         <v>-5.2999999999999999E-2</v>
       </c>
-      <c r="E260" s="33">
+      <c r="E260" s="2">
         <v>-3.4099999999999998E-2</v>
       </c>
-      <c r="F260" s="32"/>
-      <c r="G260" s="32"/>
-      <c r="H260" s="2"/>
-      <c r="I260" s="2"/>
-      <c r="J260" s="6"/>
-      <c r="K260" s="7"/>
-    </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" s="5">
         <v>37469</v>
       </c>
@@ -6794,17 +5004,11 @@
       <c r="D261" s="2">
         <v>-2.4399999999999998E-2</v>
       </c>
-      <c r="E261" s="33">
+      <c r="E261" s="2">
         <v>2.4900000000000002E-2</v>
       </c>
-      <c r="F261" s="32"/>
-      <c r="G261" s="32"/>
-      <c r="H261" s="2"/>
-      <c r="I261" s="2"/>
-      <c r="J261" s="6"/>
-      <c r="K261" s="7"/>
-    </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" s="5">
         <v>37500</v>
       </c>
@@ -6817,17 +5021,11 @@
       <c r="D262" s="2">
         <v>2.5699999999999997E-2</v>
       </c>
-      <c r="E262" s="33">
+      <c r="E262" s="2">
         <v>1.3100000000000001E-2</v>
       </c>
-      <c r="F262" s="32"/>
-      <c r="G262" s="32"/>
-      <c r="H262" s="2"/>
-      <c r="I262" s="2"/>
-      <c r="J262" s="6"/>
-      <c r="K262" s="7"/>
-    </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" s="5">
         <v>37530</v>
       </c>
@@ -6840,17 +5038,11 @@
       <c r="D263" s="2">
         <v>-2.8999999999999998E-2</v>
       </c>
-      <c r="E263" s="33">
+      <c r="E263" s="2">
         <v>-5.4600000000000003E-2</v>
       </c>
-      <c r="F263" s="32"/>
-      <c r="G263" s="32"/>
-      <c r="H263" s="2"/>
-      <c r="I263" s="2"/>
-      <c r="J263" s="6"/>
-      <c r="K263" s="7"/>
-    </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" s="5">
         <v>37561</v>
       </c>
@@ -6863,17 +5055,11 @@
       <c r="D264" s="2">
         <v>2.8399999999999998E-2</v>
       </c>
-      <c r="E264" s="33">
+      <c r="E264" s="2">
         <v>-1.15E-2</v>
       </c>
-      <c r="F264" s="32"/>
-      <c r="G264" s="32"/>
-      <c r="H264" s="2"/>
-      <c r="I264" s="2"/>
-      <c r="J264" s="6"/>
-      <c r="K264" s="7"/>
-    </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" s="5">
         <v>37591</v>
       </c>
@@ -6886,17 +5072,11 @@
       <c r="D265" s="2">
         <v>0</v>
       </c>
-      <c r="E265" s="33">
+      <c r="E265" s="2">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="F265" s="32"/>
-      <c r="G265" s="32"/>
-      <c r="H265" s="2"/>
-      <c r="I265" s="2"/>
-      <c r="J265" s="6"/>
-      <c r="K265" s="7"/>
-    </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" s="5">
         <v>37622</v>
       </c>
@@ -6909,17 +5089,11 @@
       <c r="D266" s="2">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="E266" s="33">
+      <c r="E266" s="2">
         <v>-9.300000000000001E-3</v>
       </c>
-      <c r="F266" s="32"/>
-      <c r="G266" s="32"/>
-      <c r="H266" s="2"/>
-      <c r="I266" s="2"/>
-      <c r="J266" s="6"/>
-      <c r="K266" s="7"/>
-    </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" s="5">
         <v>37653</v>
       </c>
@@ -6932,17 +5106,11 @@
       <c r="D267" s="2">
         <v>-3.4000000000000002E-3</v>
       </c>
-      <c r="E267" s="33">
+      <c r="E267" s="2">
         <v>-1.4499999999999999E-2</v>
       </c>
-      <c r="F267" s="32"/>
-      <c r="G267" s="32"/>
-      <c r="H267" s="2"/>
-      <c r="I267" s="2"/>
-      <c r="J267" s="6"/>
-      <c r="K267" s="7"/>
-    </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" s="5">
         <v>37681</v>
       </c>
@@ -6955,17 +5123,11 @@
       <c r="D268" s="2">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="E268" s="33">
+      <c r="E268" s="2">
         <v>-2.0899999999999998E-2</v>
       </c>
-      <c r="F268" s="32"/>
-      <c r="G268" s="32"/>
-      <c r="H268" s="2"/>
-      <c r="I268" s="2"/>
-      <c r="J268" s="6"/>
-      <c r="K268" s="7"/>
-    </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" s="5">
         <v>37712</v>
       </c>
@@ -6978,17 +5140,11 @@
       <c r="D269" s="2">
         <v>5.6999999999999993E-3</v>
       </c>
-      <c r="E269" s="33">
+      <c r="E269" s="2">
         <v>1.03E-2</v>
       </c>
-      <c r="F269" s="32"/>
-      <c r="G269" s="32"/>
-      <c r="H269" s="2"/>
-      <c r="I269" s="2"/>
-      <c r="J269" s="6"/>
-      <c r="K269" s="7"/>
-    </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" s="5">
         <v>37742</v>
       </c>
@@ -7001,17 +5157,11 @@
       <c r="D270" s="2">
         <v>4.7E-2</v>
       </c>
-      <c r="E270" s="33">
+      <c r="E270" s="2">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="F270" s="32"/>
-      <c r="G270" s="32"/>
-      <c r="H270" s="2"/>
-      <c r="I270" s="2"/>
-      <c r="J270" s="6"/>
-      <c r="K270" s="7"/>
-    </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" s="5">
         <v>37773</v>
       </c>
@@ -7024,17 +5174,11 @@
       <c r="D271" s="2">
         <v>1.67E-2</v>
       </c>
-      <c r="E271" s="33">
+      <c r="E271" s="2">
         <v>6.6E-3</v>
       </c>
-      <c r="F271" s="32"/>
-      <c r="G271" s="32"/>
-      <c r="H271" s="2"/>
-      <c r="I271" s="2"/>
-      <c r="J271" s="6"/>
-      <c r="K271" s="7"/>
-    </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272" s="5">
         <v>37803</v>
       </c>
@@ -7047,17 +5191,11 @@
       <c r="D272" s="2">
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="E272" s="33">
+      <c r="E272" s="2">
         <v>-1.15E-2</v>
       </c>
-      <c r="F272" s="32"/>
-      <c r="G272" s="32"/>
-      <c r="H272" s="2"/>
-      <c r="I272" s="2"/>
-      <c r="J272" s="6"/>
-      <c r="K272" s="7"/>
-    </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273" s="5">
         <v>37834</v>
       </c>
@@ -7070,17 +5208,11 @@
       <c r="D273" s="2">
         <v>2.6000000000000002E-2</v>
       </c>
-      <c r="E273" s="33">
+      <c r="E273" s="2">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="F273" s="32"/>
-      <c r="G273" s="32"/>
-      <c r="H273" s="2"/>
-      <c r="I273" s="2"/>
-      <c r="J273" s="6"/>
-      <c r="K273" s="7"/>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" s="5">
         <v>37865</v>
       </c>
@@ -7093,17 +5225,11 @@
       <c r="D274" s="2">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="E274" s="33">
+      <c r="E274" s="2">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="F274" s="32"/>
-      <c r="G274" s="32"/>
-      <c r="H274" s="2"/>
-      <c r="I274" s="2"/>
-      <c r="J274" s="6"/>
-      <c r="K274" s="7"/>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" s="5">
         <v>37895</v>
       </c>
@@ -7116,17 +5242,11 @@
       <c r="D275" s="2">
         <v>2.6800000000000001E-2</v>
       </c>
-      <c r="E275" s="33">
+      <c r="E275" s="2">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="F275" s="32"/>
-      <c r="G275" s="32"/>
-      <c r="H275" s="2"/>
-      <c r="I275" s="2"/>
-      <c r="J275" s="6"/>
-      <c r="K275" s="7"/>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" s="5">
         <v>37926</v>
       </c>
@@ -7139,17 +5259,11 @@
       <c r="D276" s="2">
         <v>2.0099999999999996E-2</v>
       </c>
-      <c r="E276" s="33">
+      <c r="E276" s="2">
         <v>1.8600000000000002E-2</v>
       </c>
-      <c r="F276" s="32"/>
-      <c r="G276" s="32"/>
-      <c r="H276" s="2"/>
-      <c r="I276" s="2"/>
-      <c r="J276" s="6"/>
-      <c r="K276" s="7"/>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" s="5">
         <v>37956</v>
       </c>
@@ -7162,17 +5276,11 @@
       <c r="D277" s="2">
         <v>-3.0099999999999998E-2</v>
       </c>
-      <c r="E277" s="33">
+      <c r="E277" s="2">
         <v>2.4199999999999999E-2</v>
       </c>
-      <c r="F277" s="32"/>
-      <c r="G277" s="32"/>
-      <c r="H277" s="2"/>
-      <c r="I277" s="2"/>
-      <c r="J277" s="6"/>
-      <c r="K277" s="7"/>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" s="5">
         <v>37987</v>
       </c>
@@ -7185,17 +5293,11 @@
       <c r="D278" s="2">
         <v>2.7999999999999997E-2</v>
       </c>
-      <c r="E278" s="33">
+      <c r="E278" s="2">
         <v>1.9799999999999998E-2</v>
       </c>
-      <c r="F278" s="32"/>
-      <c r="G278" s="32"/>
-      <c r="H278" s="2"/>
-      <c r="I278" s="2"/>
-      <c r="J278" s="6"/>
-      <c r="K278" s="7"/>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" s="5">
         <v>38018</v>
       </c>
@@ -7208,17 +5310,11 @@
       <c r="D279" s="2">
         <v>-1.43E-2</v>
       </c>
-      <c r="E279" s="33">
+      <c r="E279" s="2">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="F279" s="32"/>
-      <c r="G279" s="32"/>
-      <c r="H279" s="2"/>
-      <c r="I279" s="2"/>
-      <c r="J279" s="6"/>
-      <c r="K279" s="7"/>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" s="5">
         <v>38047</v>
       </c>
@@ -7231,17 +5327,11 @@
       <c r="D280" s="2">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="E280" s="33">
+      <c r="E280" s="2">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="F280" s="32"/>
-      <c r="G280" s="32"/>
-      <c r="H280" s="2"/>
-      <c r="I280" s="2"/>
-      <c r="J280" s="6"/>
-      <c r="K280" s="7"/>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" s="5">
         <v>38078</v>
       </c>
@@ -7254,17 +5344,11 @@
       <c r="D281" s="2">
         <v>-2.06E-2</v>
       </c>
-      <c r="E281" s="33">
+      <c r="E281" s="2">
         <v>-2.6200000000000001E-2</v>
       </c>
-      <c r="F281" s="32"/>
-      <c r="G281" s="32"/>
-      <c r="H281" s="2"/>
-      <c r="I281" s="2"/>
-      <c r="J281" s="6"/>
-      <c r="K281" s="7"/>
-    </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" s="5">
         <v>38108</v>
       </c>
@@ -7277,17 +5361,11 @@
       <c r="D282" s="2">
         <v>-2.0999999999999999E-3</v>
       </c>
-      <c r="E282" s="33">
+      <c r="E282" s="2">
         <v>-3.9000000000000003E-3</v>
       </c>
-      <c r="F282" s="32"/>
-      <c r="G282" s="32"/>
-      <c r="H282" s="2"/>
-      <c r="I282" s="2"/>
-      <c r="J282" s="6"/>
-      <c r="K282" s="7"/>
-    </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" s="5">
         <v>38139</v>
       </c>
@@ -7300,17 +5378,11 @@
       <c r="D283" s="2">
         <v>2.2599999999999999E-2</v>
       </c>
-      <c r="E283" s="33">
+      <c r="E283" s="2">
         <v>1.38E-2</v>
       </c>
-      <c r="F283" s="32"/>
-      <c r="G283" s="32"/>
-      <c r="H283" s="2"/>
-      <c r="I283" s="2"/>
-      <c r="J283" s="6"/>
-      <c r="K283" s="7"/>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" s="5">
         <v>38169</v>
       </c>
@@ -7323,17 +5395,11 @@
       <c r="D284" s="2">
         <v>-3.7900000000000003E-2</v>
       </c>
-      <c r="E284" s="33">
+      <c r="E284" s="2">
         <v>4.1100000000000005E-2</v>
       </c>
-      <c r="F284" s="32"/>
-      <c r="G284" s="32"/>
-      <c r="H284" s="2"/>
-      <c r="I284" s="2"/>
-      <c r="J284" s="6"/>
-      <c r="K284" s="7"/>
-    </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" s="5">
         <v>38200</v>
       </c>
@@ -7346,17 +5412,11 @@
       <c r="D285" s="2">
         <v>-1.6299999999999999E-2</v>
       </c>
-      <c r="E285" s="33">
+      <c r="E285" s="2">
         <v>1.03E-2</v>
       </c>
-      <c r="F285" s="32"/>
-      <c r="G285" s="32"/>
-      <c r="H285" s="2"/>
-      <c r="I285" s="2"/>
-      <c r="J285" s="6"/>
-      <c r="K285" s="7"/>
-    </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" s="5">
         <v>38231</v>
       </c>
@@ -7369,17 +5429,11 @@
       <c r="D286" s="2">
         <v>3.04E-2</v>
       </c>
-      <c r="E286" s="33">
+      <c r="E286" s="2">
         <v>-2.5000000000000001E-3</v>
       </c>
-      <c r="F286" s="32"/>
-      <c r="G286" s="32"/>
-      <c r="H286" s="2"/>
-      <c r="I286" s="2"/>
-      <c r="J286" s="6"/>
-      <c r="K286" s="7"/>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" s="5">
         <v>38261</v>
       </c>
@@ -7392,17 +5446,11 @@
       <c r="D287" s="2">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="E287" s="33">
+      <c r="E287" s="2">
         <v>-6.1999999999999998E-3</v>
       </c>
-      <c r="F287" s="32"/>
-      <c r="G287" s="32"/>
-      <c r="H287" s="2"/>
-      <c r="I287" s="2"/>
-      <c r="J287" s="6"/>
-      <c r="K287" s="7"/>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" s="5">
         <v>38292</v>
       </c>
@@ -7415,17 +5463,11 @@
       <c r="D288" s="2">
         <v>3.9100000000000003E-2</v>
       </c>
-      <c r="E288" s="33">
+      <c r="E288" s="2">
         <v>1.8000000000000002E-2</v>
       </c>
-      <c r="F288" s="32"/>
-      <c r="G288" s="32"/>
-      <c r="H288" s="2"/>
-      <c r="I288" s="2"/>
-      <c r="J288" s="6"/>
-      <c r="K288" s="7"/>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" s="5">
         <v>38322</v>
       </c>
@@ -7438,17 +5480,11 @@
       <c r="D289" s="2">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="E289" s="33">
+      <c r="E289" s="2">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="F289" s="32"/>
-      <c r="G289" s="32"/>
-      <c r="H289" s="2"/>
-      <c r="I289" s="2"/>
-      <c r="J289" s="6"/>
-      <c r="K289" s="7"/>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" s="5">
         <v>38353</v>
       </c>
@@ -7461,17 +5497,11 @@
       <c r="D290" s="2">
         <v>-1.52E-2</v>
       </c>
-      <c r="E290" s="33">
+      <c r="E290" s="2">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="F290" s="32"/>
-      <c r="G290" s="32"/>
-      <c r="H290" s="2"/>
-      <c r="I290" s="2"/>
-      <c r="J290" s="6"/>
-      <c r="K290" s="7"/>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" s="5">
         <v>38384</v>
       </c>
@@ -7484,17 +5514,11 @@
       <c r="D291" s="2">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E291" s="33">
+      <c r="E291" s="2">
         <v>1.6399999999999998E-2</v>
       </c>
-      <c r="F291" s="32"/>
-      <c r="G291" s="32"/>
-      <c r="H291" s="2"/>
-      <c r="I291" s="2"/>
-      <c r="J291" s="6"/>
-      <c r="K291" s="7"/>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" s="5">
         <v>38412</v>
       </c>
@@ -7507,17 +5531,11 @@
       <c r="D292" s="2">
         <v>-1.3999999999999999E-2</v>
       </c>
-      <c r="E292" s="33">
+      <c r="E292" s="2">
         <v>1.5600000000000001E-2</v>
       </c>
-      <c r="F292" s="32"/>
-      <c r="G292" s="32"/>
-      <c r="H292" s="2"/>
-      <c r="I292" s="2"/>
-      <c r="J292" s="6"/>
-      <c r="K292" s="7"/>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293" s="5">
         <v>38443</v>
       </c>
@@ -7530,17 +5548,11 @@
       <c r="D293" s="2">
         <v>-0.04</v>
       </c>
-      <c r="E293" s="33">
+      <c r="E293" s="2">
         <v>-3.4999999999999996E-3</v>
       </c>
-      <c r="F293" s="32"/>
-      <c r="G293" s="32"/>
-      <c r="H293" s="2"/>
-      <c r="I293" s="2"/>
-      <c r="J293" s="6"/>
-      <c r="K293" s="7"/>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" s="5">
         <v>38473</v>
       </c>
@@ -7553,17 +5565,11 @@
       <c r="D294" s="2">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="E294" s="33">
+      <c r="E294" s="2">
         <v>-8.3000000000000001E-3</v>
       </c>
-      <c r="F294" s="32"/>
-      <c r="G294" s="32"/>
-      <c r="H294" s="2"/>
-      <c r="I294" s="2"/>
-      <c r="J294" s="6"/>
-      <c r="K294" s="7"/>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" s="5">
         <v>38504</v>
       </c>
@@ -7576,17 +5582,11 @@
       <c r="D295" s="2">
         <v>2.6200000000000001E-2</v>
       </c>
-      <c r="E295" s="33">
+      <c r="E295" s="2">
         <v>2.6200000000000001E-2</v>
       </c>
-      <c r="F295" s="32"/>
-      <c r="G295" s="32"/>
-      <c r="H295" s="2"/>
-      <c r="I295" s="2"/>
-      <c r="J295" s="6"/>
-      <c r="K295" s="7"/>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" s="5">
         <v>38534</v>
       </c>
@@ -7599,17 +5599,11 @@
       <c r="D296" s="2">
         <v>2.9300000000000003E-2</v>
       </c>
-      <c r="E296" s="33">
+      <c r="E296" s="2">
         <v>-5.1000000000000004E-3</v>
       </c>
-      <c r="F296" s="32"/>
-      <c r="G296" s="32"/>
-      <c r="H296" s="2"/>
-      <c r="I296" s="2"/>
-      <c r="J296" s="6"/>
-      <c r="K296" s="7"/>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" s="5">
         <v>38565</v>
       </c>
@@ -7622,17 +5616,11 @@
       <c r="D297" s="2">
         <v>-9.1999999999999998E-3</v>
       </c>
-      <c r="E297" s="33">
+      <c r="E297" s="2">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="F297" s="32"/>
-      <c r="G297" s="32"/>
-      <c r="H297" s="2"/>
-      <c r="I297" s="2"/>
-      <c r="J297" s="6"/>
-      <c r="K297" s="7"/>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" s="5">
         <v>38596</v>
       </c>
@@ -7645,17 +5633,11 @@
       <c r="D298" s="2">
         <v>-5.7999999999999996E-3</v>
       </c>
-      <c r="E298" s="33">
+      <c r="E298" s="2">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="F298" s="32"/>
-      <c r="G298" s="32"/>
-      <c r="H298" s="2"/>
-      <c r="I298" s="2"/>
-      <c r="J298" s="6"/>
-      <c r="K298" s="7"/>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" s="5">
         <v>38626</v>
       </c>
@@ -7668,17 +5650,11 @@
       <c r="D299" s="2">
         <v>-1.21E-2</v>
       </c>
-      <c r="E299" s="33">
+      <c r="E299" s="2">
         <v>2.3E-3</v>
       </c>
-      <c r="F299" s="32"/>
-      <c r="G299" s="32"/>
-      <c r="H299" s="2"/>
-      <c r="I299" s="2"/>
-      <c r="J299" s="6"/>
-      <c r="K299" s="7"/>
-    </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" s="5">
         <v>38657</v>
       </c>
@@ -7691,17 +5667,11 @@
       <c r="D300" s="2">
         <v>9.1000000000000004E-3</v>
       </c>
-      <c r="E300" s="33">
+      <c r="E300" s="2">
         <v>-1.18E-2</v>
       </c>
-      <c r="F300" s="32"/>
-      <c r="G300" s="32"/>
-      <c r="H300" s="2"/>
-      <c r="I300" s="2"/>
-      <c r="J300" s="6"/>
-      <c r="K300" s="7"/>
-    </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" s="5">
         <v>38687</v>
       </c>
@@ -7714,17 +5684,11 @@
       <c r="D301" s="2">
         <v>-4.5999999999999999E-3</v>
       </c>
-      <c r="E301" s="33">
+      <c r="E301" s="2">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="F301" s="32"/>
-      <c r="G301" s="32"/>
-      <c r="H301" s="2"/>
-      <c r="I301" s="2"/>
-      <c r="J301" s="6"/>
-      <c r="K301" s="7"/>
-    </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" s="5">
         <v>38718</v>
       </c>
@@ -7737,17 +5701,11 @@
       <c r="D302" s="2">
         <v>5.4199999999999998E-2</v>
       </c>
-      <c r="E302" s="33">
+      <c r="E302" s="2">
         <v>1.1200000000000002E-2</v>
       </c>
-      <c r="F302" s="32"/>
-      <c r="G302" s="32"/>
-      <c r="H302" s="2"/>
-      <c r="I302" s="2"/>
-      <c r="J302" s="6"/>
-      <c r="K302" s="7"/>
-    </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" s="5">
         <v>38749</v>
       </c>
@@ -7760,17 +5718,11 @@
       <c r="D303" s="2">
         <v>-3.8E-3</v>
       </c>
-      <c r="E303" s="33">
+      <c r="E303" s="2">
         <v>-2.5000000000000001E-3</v>
       </c>
-      <c r="F303" s="32"/>
-      <c r="G303" s="32"/>
-      <c r="H303" s="2"/>
-      <c r="I303" s="2"/>
-      <c r="J303" s="6"/>
-      <c r="K303" s="7"/>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" s="5">
         <v>38777</v>
       </c>
@@ -7783,17 +5735,11 @@
       <c r="D304" s="2">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="E304" s="33">
+      <c r="E304" s="2">
         <v>6.0999999999999995E-3</v>
       </c>
-      <c r="F304" s="32"/>
-      <c r="G304" s="32"/>
-      <c r="H304" s="2"/>
-      <c r="I304" s="2"/>
-      <c r="J304" s="6"/>
-      <c r="K304" s="7"/>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" s="5">
         <v>38808</v>
       </c>
@@ -7806,17 +5752,11 @@
       <c r="D305" s="2">
         <v>-1.34E-2</v>
       </c>
-      <c r="E305" s="33">
+      <c r="E305" s="2">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="F305" s="32"/>
-      <c r="G305" s="32"/>
-      <c r="H305" s="2"/>
-      <c r="I305" s="2"/>
-      <c r="J305" s="6"/>
-      <c r="K305" s="7"/>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306" s="5">
         <v>38838</v>
       </c>
@@ -7829,17 +5769,11 @@
       <c r="D306" s="2">
         <v>-3.04E-2</v>
       </c>
-      <c r="E306" s="33">
+      <c r="E306" s="2">
         <v>2.5499999999999998E-2</v>
       </c>
-      <c r="F306" s="32"/>
-      <c r="G306" s="32"/>
-      <c r="H306" s="2"/>
-      <c r="I306" s="2"/>
-      <c r="J306" s="6"/>
-      <c r="K306" s="7"/>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" s="5">
         <v>38869</v>
       </c>
@@ -7852,17 +5786,11 @@
       <c r="D307" s="2">
         <v>-3.4999999999999996E-3</v>
       </c>
-      <c r="E307" s="33">
+      <c r="E307" s="2">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="F307" s="32"/>
-      <c r="G307" s="32"/>
-      <c r="H307" s="2"/>
-      <c r="I307" s="2"/>
-      <c r="J307" s="6"/>
-      <c r="K307" s="7"/>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308" s="5">
         <v>38899</v>
       </c>
@@ -7875,17 +5803,11 @@
       <c r="D308" s="2">
         <v>-4.0800000000000003E-2</v>
       </c>
-      <c r="E308" s="33">
+      <c r="E308" s="2">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="F308" s="32"/>
-      <c r="G308" s="32"/>
-      <c r="H308" s="2"/>
-      <c r="I308" s="2"/>
-      <c r="J308" s="6"/>
-      <c r="K308" s="7"/>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="5">
         <v>38930</v>
       </c>
@@ -7898,17 +5820,11 @@
       <c r="D309" s="2">
         <v>9.0000000000000011E-3</v>
       </c>
-      <c r="E309" s="33">
+      <c r="E309" s="2">
         <v>-1.72E-2</v>
       </c>
-      <c r="F309" s="32"/>
-      <c r="G309" s="32"/>
-      <c r="H309" s="2"/>
-      <c r="I309" s="2"/>
-      <c r="J309" s="6"/>
-      <c r="K309" s="7"/>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" s="5">
         <v>38961</v>
       </c>
@@ -7921,17 +5837,11 @@
       <c r="D310" s="2">
         <v>-1.37E-2</v>
       </c>
-      <c r="E310" s="33">
+      <c r="E310" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="F310" s="32"/>
-      <c r="G310" s="32"/>
-      <c r="H310" s="2"/>
-      <c r="I310" s="2"/>
-      <c r="J310" s="6"/>
-      <c r="K310" s="7"/>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="5">
         <v>38991</v>
       </c>
@@ -7944,17 +5854,11 @@
       <c r="D311" s="2">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="E311" s="33">
+      <c r="E311" s="2">
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="F311" s="32"/>
-      <c r="G311" s="32"/>
-      <c r="H311" s="2"/>
-      <c r="I311" s="2"/>
-      <c r="J311" s="6"/>
-      <c r="K311" s="7"/>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="5">
         <v>39022</v>
       </c>
@@ -7967,17 +5871,11 @@
       <c r="D312" s="2">
         <v>8.6E-3</v>
       </c>
-      <c r="E312" s="33">
+      <c r="E312" s="2">
         <v>7.000000000000001E-4</v>
       </c>
-      <c r="F312" s="32"/>
-      <c r="G312" s="32"/>
-      <c r="H312" s="2"/>
-      <c r="I312" s="2"/>
-      <c r="J312" s="6"/>
-      <c r="K312" s="7"/>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313" s="5">
         <v>39052</v>
       </c>
@@ -7990,17 +5888,11 @@
       <c r="D313" s="2">
         <v>-1.1000000000000001E-2</v>
       </c>
-      <c r="E313" s="33">
+      <c r="E313" s="2">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="F313" s="32"/>
-      <c r="G313" s="32"/>
-      <c r="H313" s="2"/>
-      <c r="I313" s="2"/>
-      <c r="J313" s="6"/>
-      <c r="K313" s="7"/>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="5">
         <v>39083</v>
       </c>
@@ -8013,17 +5905,11 @@
       <c r="D314" s="2">
         <v>1E-3</v>
       </c>
-      <c r="E314" s="33">
+      <c r="E314" s="2">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="F314" s="32"/>
-      <c r="G314" s="32"/>
-      <c r="H314" s="2"/>
-      <c r="I314" s="2"/>
-      <c r="J314" s="6"/>
-      <c r="K314" s="7"/>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315" s="5">
         <v>39114</v>
       </c>
@@ -8036,17 +5922,11 @@
       <c r="D315" s="2">
         <v>1.32E-2</v>
       </c>
-      <c r="E315" s="33">
+      <c r="E315" s="2">
         <v>-8.9999999999999998E-4</v>
       </c>
-      <c r="F315" s="32"/>
-      <c r="G315" s="32"/>
-      <c r="H315" s="2"/>
-      <c r="I315" s="2"/>
-      <c r="J315" s="6"/>
-      <c r="K315" s="7"/>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316" s="5">
         <v>39142</v>
       </c>
@@ -8059,17 +5939,11 @@
       <c r="D316" s="2">
         <v>-5.9999999999999995E-4</v>
       </c>
-      <c r="E316" s="33">
+      <c r="E316" s="2">
         <v>-2.2000000000000001E-3</v>
       </c>
-      <c r="F316" s="32"/>
-      <c r="G316" s="32"/>
-      <c r="H316" s="2"/>
-      <c r="I316" s="2"/>
-      <c r="J316" s="6"/>
-      <c r="K316" s="7"/>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" s="5">
         <v>39173</v>
       </c>
@@ -8082,17 +5956,11 @@
       <c r="D317" s="2">
         <v>-2.06E-2</v>
       </c>
-      <c r="E317" s="33">
+      <c r="E317" s="2">
         <v>-1.15E-2</v>
       </c>
-      <c r="F317" s="32"/>
-      <c r="G317" s="32"/>
-      <c r="H317" s="2"/>
-      <c r="I317" s="2"/>
-      <c r="J317" s="6"/>
-      <c r="K317" s="7"/>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" s="5">
         <v>39203</v>
       </c>
@@ -8105,17 +5973,11 @@
       <c r="D318" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="E318" s="33">
+      <c r="E318" s="2">
         <v>-5.0000000000000001E-4</v>
       </c>
-      <c r="F318" s="32"/>
-      <c r="G318" s="32"/>
-      <c r="H318" s="2"/>
-      <c r="I318" s="2"/>
-      <c r="J318" s="6"/>
-      <c r="K318" s="7"/>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319" s="5">
         <v>39234</v>
       </c>
@@ -8128,17 +5990,11 @@
       <c r="D319" s="2">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="E319" s="33">
+      <c r="E319" s="2">
         <v>-1.1299999999999999E-2</v>
       </c>
-      <c r="F319" s="32"/>
-      <c r="G319" s="32"/>
-      <c r="H319" s="2"/>
-      <c r="I319" s="2"/>
-      <c r="J319" s="6"/>
-      <c r="K319" s="7"/>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" s="5">
         <v>39264</v>
       </c>
@@ -8151,17 +6007,11 @@
       <c r="D320" s="2">
         <v>-2.5099999999999997E-2</v>
       </c>
-      <c r="E320" s="33">
+      <c r="E320" s="2">
         <v>-3.3399999999999999E-2</v>
       </c>
-      <c r="F320" s="32"/>
-      <c r="G320" s="32"/>
-      <c r="H320" s="2"/>
-      <c r="I320" s="2"/>
-      <c r="J320" s="6"/>
-      <c r="K320" s="7"/>
-    </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321" s="5">
         <v>39295</v>
       </c>
@@ -8174,17 +6024,11 @@
       <c r="D321" s="2">
         <v>-1.2999999999999999E-3</v>
       </c>
-      <c r="E321" s="33">
+      <c r="E321" s="2">
         <v>-2.2400000000000003E-2</v>
       </c>
-      <c r="F321" s="32"/>
-      <c r="G321" s="32"/>
-      <c r="H321" s="2"/>
-      <c r="I321" s="2"/>
-      <c r="J321" s="6"/>
-      <c r="K321" s="7"/>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" s="5">
         <v>39326</v>
       </c>
@@ -8197,17 +6041,11 @@
       <c r="D322" s="2">
         <v>-2.29E-2</v>
       </c>
-      <c r="E322" s="33">
+      <c r="E322" s="2">
         <v>-1.8600000000000002E-2</v>
       </c>
-      <c r="F322" s="32"/>
-      <c r="G322" s="32"/>
-      <c r="H322" s="2"/>
-      <c r="I322" s="2"/>
-      <c r="J322" s="6"/>
-      <c r="K322" s="7"/>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" s="5">
         <v>39356</v>
       </c>
@@ -8220,17 +6058,11 @@
       <c r="D323" s="2">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="E323" s="33">
+      <c r="E323" s="2">
         <v>-2.5899999999999999E-2</v>
       </c>
-      <c r="F323" s="32"/>
-      <c r="G323" s="32"/>
-      <c r="H323" s="2"/>
-      <c r="I323" s="2"/>
-      <c r="J323" s="6"/>
-      <c r="K323" s="7"/>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" s="5">
         <v>39387</v>
       </c>
@@ -8243,17 +6075,11 @@
       <c r="D324" s="2">
         <v>-2.63E-2</v>
       </c>
-      <c r="E324" s="33">
+      <c r="E324" s="2">
         <v>-1.18E-2</v>
       </c>
-      <c r="F324" s="32"/>
-      <c r="G324" s="32"/>
-      <c r="H324" s="2"/>
-      <c r="I324" s="2"/>
-      <c r="J324" s="6"/>
-      <c r="K324" s="7"/>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" s="5">
         <v>39417</v>
       </c>
@@ -8266,17 +6092,11 @@
       <c r="D325" s="2">
         <v>2E-3</v>
       </c>
-      <c r="E325" s="33">
+      <c r="E325" s="2">
         <v>-5.1999999999999998E-3</v>
       </c>
-      <c r="F325" s="32"/>
-      <c r="G325" s="32"/>
-      <c r="H325" s="2"/>
-      <c r="I325" s="2"/>
-      <c r="J325" s="6"/>
-      <c r="K325" s="7"/>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" s="5">
         <v>39448</v>
       </c>
@@ -8289,17 +6109,11 @@
       <c r="D326" s="2">
         <v>-8.8999999999999999E-3</v>
       </c>
-      <c r="E326" s="33">
+      <c r="E326" s="2">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="F326" s="32"/>
-      <c r="G326" s="32"/>
-      <c r="H326" s="2"/>
-      <c r="I326" s="2"/>
-      <c r="J326" s="6"/>
-      <c r="K326" s="7"/>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" s="5">
         <v>39479</v>
       </c>
@@ -8312,17 +6126,11 @@
       <c r="D327" s="2">
         <v>-2.3E-3</v>
       </c>
-      <c r="E327" s="33">
+      <c r="E327" s="2">
         <v>-9.3999999999999986E-3</v>
       </c>
-      <c r="F327" s="32"/>
-      <c r="G327" s="32"/>
-      <c r="H327" s="2"/>
-      <c r="I327" s="2"/>
-      <c r="J327" s="6"/>
-      <c r="K327" s="7"/>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" s="5">
         <v>39508</v>
       </c>
@@ -8335,17 +6143,11 @@
       <c r="D328" s="2">
         <v>9.3999999999999986E-3</v>
       </c>
-      <c r="E328" s="33">
+      <c r="E328" s="2">
         <v>-1.5E-3</v>
       </c>
-      <c r="F328" s="32"/>
-      <c r="G328" s="32"/>
-      <c r="H328" s="2"/>
-      <c r="I328" s="2"/>
-      <c r="J328" s="6"/>
-      <c r="K328" s="7"/>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" s="5">
         <v>39539</v>
       </c>
@@ -8358,17 +6160,11 @@
       <c r="D329" s="2">
         <v>-1.6399999999999998E-2</v>
       </c>
-      <c r="E329" s="33">
+      <c r="E329" s="2">
         <v>-9.5999999999999992E-3</v>
       </c>
-      <c r="F329" s="32"/>
-      <c r="G329" s="32"/>
-      <c r="H329" s="2"/>
-      <c r="I329" s="2"/>
-      <c r="J329" s="6"/>
-      <c r="K329" s="7"/>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" s="5">
         <v>39569</v>
       </c>
@@ -8381,17 +6177,11 @@
       <c r="D330" s="2">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="E330" s="33">
+      <c r="E330" s="2">
         <v>-1.38E-2</v>
       </c>
-      <c r="F330" s="32"/>
-      <c r="G330" s="32"/>
-      <c r="H330" s="2"/>
-      <c r="I330" s="2"/>
-      <c r="J330" s="6"/>
-      <c r="K330" s="7"/>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" s="5">
         <v>39600</v>
       </c>
@@ -8404,17 +6194,11 @@
       <c r="D331" s="2">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="E331" s="33">
+      <c r="E331" s="2">
         <v>-2.4300000000000002E-2</v>
       </c>
-      <c r="F331" s="32"/>
-      <c r="G331" s="32"/>
-      <c r="H331" s="2"/>
-      <c r="I331" s="2"/>
-      <c r="J331" s="6"/>
-      <c r="K331" s="7"/>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" s="5">
         <v>39630</v>
       </c>
@@ -8427,17 +6211,11 @@
       <c r="D332" s="2">
         <v>2.4700000000000003E-2</v>
       </c>
-      <c r="E332" s="33">
+      <c r="E332" s="2">
         <v>5.8099999999999999E-2</v>
       </c>
-      <c r="F332" s="32"/>
-      <c r="G332" s="32"/>
-      <c r="H332" s="2"/>
-      <c r="I332" s="2"/>
-      <c r="J332" s="6"/>
-      <c r="K332" s="7"/>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" s="5">
         <v>39661</v>
       </c>
@@ -8450,17 +6228,11 @@
       <c r="D333" s="2">
         <v>3.61E-2</v>
       </c>
-      <c r="E333" s="33">
+      <c r="E333" s="2">
         <v>1.5600000000000001E-2</v>
       </c>
-      <c r="F333" s="32"/>
-      <c r="G333" s="32"/>
-      <c r="H333" s="2"/>
-      <c r="I333" s="2"/>
-      <c r="J333" s="6"/>
-      <c r="K333" s="7"/>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" s="5">
         <v>39692</v>
       </c>
@@ -8473,17 +6245,11 @@
       <c r="D334" s="2">
         <v>-1.1299999999999999E-2</v>
       </c>
-      <c r="E334" s="33">
+      <c r="E334" s="2">
         <v>6.3299999999999995E-2</v>
       </c>
-      <c r="F334" s="32"/>
-      <c r="G334" s="32"/>
-      <c r="H334" s="2"/>
-      <c r="I334" s="2"/>
-      <c r="J334" s="6"/>
-      <c r="K334" s="7"/>
-    </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" s="5">
         <v>39722</v>
       </c>
@@ -8496,17 +6262,11 @@
       <c r="D335" s="2">
         <v>-2.3300000000000001E-2</v>
       </c>
-      <c r="E335" s="33">
+      <c r="E335" s="2">
         <v>-2.8999999999999998E-2</v>
       </c>
-      <c r="F335" s="32"/>
-      <c r="G335" s="32"/>
-      <c r="H335" s="2"/>
-      <c r="I335" s="2"/>
-      <c r="J335" s="6"/>
-      <c r="K335" s="7"/>
-    </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" s="5">
         <v>39753</v>
       </c>
@@ -8519,17 +6279,11 @@
       <c r="D336" s="2">
         <v>-2.9900000000000003E-2</v>
       </c>
-      <c r="E336" s="33">
+      <c r="E336" s="2">
         <v>-5.9400000000000001E-2</v>
       </c>
-      <c r="F336" s="32"/>
-      <c r="G336" s="32"/>
-      <c r="H336" s="2"/>
-      <c r="I336" s="2"/>
-      <c r="J336" s="6"/>
-      <c r="K336" s="7"/>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="5">
         <v>39783</v>
       </c>
@@ -8542,17 +6296,11 @@
       <c r="D337" s="2">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E337" s="33">
+      <c r="E337" s="2">
         <v>-2.3999999999999998E-3</v>
       </c>
-      <c r="F337" s="32"/>
-      <c r="G337" s="32"/>
-      <c r="H337" s="2"/>
-      <c r="I337" s="2"/>
-      <c r="J337" s="6"/>
-      <c r="K337" s="7"/>
-    </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="5">
         <v>39814</v>
       </c>
@@ -8565,17 +6313,11 @@
       <c r="D338" s="2">
         <v>-1E-4</v>
       </c>
-      <c r="E338" s="33">
+      <c r="E338" s="2">
         <v>-0.111</v>
       </c>
-      <c r="F338" s="32"/>
-      <c r="G338" s="32"/>
-      <c r="H338" s="2"/>
-      <c r="I338" s="2"/>
-      <c r="J338" s="6"/>
-      <c r="K338" s="7"/>
-    </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="5">
         <v>39845</v>
       </c>
@@ -8588,17 +6330,11 @@
       <c r="D339" s="2">
         <v>1.7000000000000001E-3</v>
       </c>
-      <c r="E339" s="33">
+      <c r="E339" s="2">
         <v>-7.2499999999999995E-2</v>
       </c>
-      <c r="F339" s="32"/>
-      <c r="G339" s="32"/>
-      <c r="H339" s="2"/>
-      <c r="I339" s="2"/>
-      <c r="J339" s="6"/>
-      <c r="K339" s="7"/>
-    </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="5">
         <v>39873</v>
       </c>
@@ -8611,17 +6347,11 @@
       <c r="D340" s="2">
         <v>-8.9999999999999998E-4</v>
       </c>
-      <c r="E340" s="33">
+      <c r="E340" s="2">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="F340" s="32"/>
-      <c r="G340" s="32"/>
-      <c r="H340" s="2"/>
-      <c r="I340" s="2"/>
-      <c r="J340" s="6"/>
-      <c r="K340" s="7"/>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="5">
         <v>39904</v>
       </c>
@@ -8634,17 +6364,11 @@
       <c r="D341" s="2">
         <v>4.8300000000000003E-2</v>
       </c>
-      <c r="E341" s="33">
+      <c r="E341" s="2">
         <v>5.4600000000000003E-2</v>
       </c>
-      <c r="F341" s="32"/>
-      <c r="G341" s="32"/>
-      <c r="H341" s="2"/>
-      <c r="I341" s="2"/>
-      <c r="J341" s="6"/>
-      <c r="K341" s="7"/>
-    </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" s="5">
         <v>39934</v>
       </c>
@@ -8657,17 +6381,11 @@
       <c r="D342" s="2">
         <v>-2.3300000000000001E-2</v>
       </c>
-      <c r="E342" s="33">
+      <c r="E342" s="2">
         <v>-2.0999999999999999E-3</v>
       </c>
-      <c r="F342" s="32"/>
-      <c r="G342" s="32"/>
-      <c r="H342" s="2"/>
-      <c r="I342" s="2"/>
-      <c r="J342" s="6"/>
-      <c r="K342" s="7"/>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" s="5">
         <v>39965</v>
       </c>
@@ -8680,17 +6398,11 @@
       <c r="D343" s="2">
         <v>2.6099999999999998E-2</v>
       </c>
-      <c r="E343" s="33">
+      <c r="E343" s="2">
         <v>-2.7099999999999999E-2</v>
       </c>
-      <c r="F343" s="32"/>
-      <c r="G343" s="32"/>
-      <c r="H343" s="2"/>
-      <c r="I343" s="2"/>
-      <c r="J343" s="6"/>
-      <c r="K343" s="7"/>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" s="5">
         <v>39995</v>
       </c>
@@ -8703,17 +6415,11 @@
       <c r="D344" s="2">
         <v>2.07E-2</v>
       </c>
-      <c r="E344" s="33">
+      <c r="E344" s="2">
         <v>5.28E-2</v>
       </c>
-      <c r="F344" s="32"/>
-      <c r="G344" s="32"/>
-      <c r="H344" s="2"/>
-      <c r="I344" s="2"/>
-      <c r="J344" s="6"/>
-      <c r="K344" s="7"/>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" s="5">
         <v>40026</v>
       </c>
@@ -8726,17 +6432,11 @@
       <c r="D345" s="2">
         <v>-9.0000000000000011E-3</v>
       </c>
-      <c r="E345" s="33">
+      <c r="E345" s="2">
         <v>7.7600000000000002E-2</v>
       </c>
-      <c r="F345" s="32"/>
-      <c r="G345" s="32"/>
-      <c r="H345" s="2"/>
-      <c r="I345" s="2"/>
-      <c r="J345" s="6"/>
-      <c r="K345" s="7"/>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" s="5">
         <v>40057</v>
       </c>
@@ -8749,17 +6449,11 @@
       <c r="D346" s="2">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="E346" s="33">
+      <c r="E346" s="2">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="F346" s="32"/>
-      <c r="G346" s="32"/>
-      <c r="H346" s="2"/>
-      <c r="I346" s="2"/>
-      <c r="J346" s="6"/>
-      <c r="K346" s="7"/>
-    </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" s="5">
         <v>40087</v>
       </c>
@@ -8772,17 +6466,11 @@
       <c r="D347" s="2">
         <v>-4.2199999999999994E-2</v>
       </c>
-      <c r="E347" s="33">
+      <c r="E347" s="2">
         <v>-4.1700000000000001E-2</v>
       </c>
-      <c r="F347" s="32"/>
-      <c r="G347" s="32"/>
-      <c r="H347" s="2"/>
-      <c r="I347" s="2"/>
-      <c r="J347" s="6"/>
-      <c r="K347" s="7"/>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" s="5">
         <v>40118</v>
       </c>
@@ -8795,17 +6483,11 @@
       <c r="D348" s="2">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="E348" s="33">
+      <c r="E348" s="2">
         <v>-1.7000000000000001E-3</v>
       </c>
-      <c r="F348" s="32"/>
-      <c r="G348" s="32"/>
-      <c r="H348" s="2"/>
-      <c r="I348" s="2"/>
-      <c r="J348" s="6"/>
-      <c r="K348" s="7"/>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" s="5">
         <v>40148</v>
       </c>
@@ -8818,17 +6500,11 @@
       <c r="D349" s="2">
         <v>6.1100000000000002E-2</v>
       </c>
-      <c r="E349" s="33">
+      <c r="E349" s="2">
         <v>1E-4</v>
       </c>
-      <c r="F349" s="32"/>
-      <c r="G349" s="32"/>
-      <c r="H349" s="2"/>
-      <c r="I349" s="2"/>
-      <c r="J349" s="6"/>
-      <c r="K349" s="7"/>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" s="5">
         <v>40179</v>
       </c>
@@ -8841,17 +6517,11 @@
       <c r="D350" s="2">
         <v>3.8E-3</v>
       </c>
-      <c r="E350" s="33">
+      <c r="E350" s="2">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="F350" s="32"/>
-      <c r="G350" s="32"/>
-      <c r="H350" s="2"/>
-      <c r="I350" s="2"/>
-      <c r="J350" s="6"/>
-      <c r="K350" s="7"/>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" s="5">
         <v>40210</v>
       </c>
@@ -8864,17 +6534,11 @@
       <c r="D351" s="2">
         <v>1.2E-2</v>
       </c>
-      <c r="E351" s="33">
+      <c r="E351" s="2">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="F351" s="32"/>
-      <c r="G351" s="32"/>
-      <c r="H351" s="2"/>
-      <c r="I351" s="2"/>
-      <c r="J351" s="6"/>
-      <c r="K351" s="7"/>
-    </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" s="5">
         <v>40238</v>
       </c>
@@ -8887,17 +6551,11 @@
       <c r="D352" s="2">
         <v>1.4199999999999999E-2</v>
       </c>
-      <c r="E352" s="33">
+      <c r="E352" s="2">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F352" s="32"/>
-      <c r="G352" s="32"/>
-      <c r="H352" s="2"/>
-      <c r="I352" s="2"/>
-      <c r="J352" s="6"/>
-      <c r="K352" s="7"/>
-    </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" s="5">
         <v>40269</v>
       </c>
@@ -8910,17 +6568,11 @@
       <c r="D353" s="2">
         <v>4.9800000000000004E-2</v>
       </c>
-      <c r="E353" s="33">
+      <c r="E353" s="2">
         <v>2.81E-2</v>
       </c>
-      <c r="F353" s="32"/>
-      <c r="G353" s="32"/>
-      <c r="H353" s="2"/>
-      <c r="I353" s="2"/>
-      <c r="J353" s="6"/>
-      <c r="K353" s="7"/>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" s="5">
         <v>40299</v>
       </c>
@@ -8933,17 +6585,11 @@
       <c r="D354" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="E354" s="33">
+      <c r="E354" s="2">
         <v>-2.3799999999999998E-2</v>
       </c>
-      <c r="F354" s="32"/>
-      <c r="G354" s="32"/>
-      <c r="H354" s="2"/>
-      <c r="I354" s="2"/>
-      <c r="J354" s="6"/>
-      <c r="K354" s="7"/>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" s="5">
         <v>40330</v>
       </c>
@@ -8956,17 +6602,11 @@
       <c r="D355" s="2">
         <v>-1.9699999999999999E-2</v>
       </c>
-      <c r="E355" s="33">
+      <c r="E355" s="2">
         <v>-4.4999999999999998E-2</v>
       </c>
-      <c r="F355" s="32"/>
-      <c r="G355" s="32"/>
-      <c r="H355" s="2"/>
-      <c r="I355" s="2"/>
-      <c r="J355" s="6"/>
-      <c r="K355" s="7"/>
-    </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" s="5">
         <v>40360</v>
       </c>
@@ -8979,17 +6619,11 @@
       <c r="D356" s="2">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="E356" s="33">
+      <c r="E356" s="2">
         <v>-2.7000000000000001E-3</v>
       </c>
-      <c r="F356" s="32"/>
-      <c r="G356" s="32"/>
-      <c r="H356" s="2"/>
-      <c r="I356" s="2"/>
-      <c r="J356" s="6"/>
-      <c r="K356" s="7"/>
-    </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" s="5">
         <v>40391</v>
       </c>
@@ -9002,17 +6636,11 @@
       <c r="D357" s="2">
         <v>-0.03</v>
       </c>
-      <c r="E357" s="33">
+      <c r="E357" s="2">
         <v>-1.95E-2</v>
       </c>
-      <c r="F357" s="32"/>
-      <c r="G357" s="32"/>
-      <c r="H357" s="2"/>
-      <c r="I357" s="2"/>
-      <c r="J357" s="6"/>
-      <c r="K357" s="7"/>
-    </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" s="5">
         <v>40422</v>
       </c>
@@ -9025,17 +6653,11 @@
       <c r="D358" s="2">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="E358" s="33">
+      <c r="E358" s="2">
         <v>-3.1200000000000002E-2</v>
       </c>
-      <c r="F358" s="32"/>
-      <c r="G358" s="32"/>
-      <c r="H358" s="2"/>
-      <c r="I358" s="2"/>
-      <c r="J358" s="6"/>
-      <c r="K358" s="7"/>
-    </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" s="5">
         <v>40452</v>
       </c>
@@ -9048,17 +6670,11 @@
       <c r="D359" s="2">
         <v>1.15E-2</v>
       </c>
-      <c r="E359" s="33">
+      <c r="E359" s="2">
         <v>-2.5899999999999999E-2</v>
       </c>
-      <c r="F359" s="32"/>
-      <c r="G359" s="32"/>
-      <c r="H359" s="2"/>
-      <c r="I359" s="2"/>
-      <c r="J359" s="6"/>
-      <c r="K359" s="7"/>
-    </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" s="5">
         <v>40483</v>
       </c>
@@ -9071,17 +6687,11 @@
       <c r="D360" s="2">
         <v>3.7000000000000005E-2</v>
       </c>
-      <c r="E360" s="33">
+      <c r="E360" s="2">
         <v>-9.0000000000000011E-3</v>
       </c>
-      <c r="F360" s="32"/>
-      <c r="G360" s="32"/>
-      <c r="H360" s="2"/>
-      <c r="I360" s="2"/>
-      <c r="J360" s="6"/>
-      <c r="K360" s="7"/>
-    </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" s="5">
         <v>40513</v>
       </c>
@@ -9094,17 +6704,11 @@
       <c r="D361" s="2">
         <v>6.9999999999999993E-3</v>
       </c>
-      <c r="E361" s="33">
+      <c r="E361" s="2">
         <v>3.8100000000000002E-2</v>
       </c>
-      <c r="F361" s="32"/>
-      <c r="G361" s="32"/>
-      <c r="H361" s="2"/>
-      <c r="I361" s="2"/>
-      <c r="J361" s="6"/>
-      <c r="K361" s="7"/>
-    </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" s="5">
         <v>40544</v>
       </c>
@@ -9117,17 +6721,11 @@
       <c r="D362" s="2">
         <v>-2.4700000000000003E-2</v>
       </c>
-      <c r="E362" s="33">
+      <c r="E362" s="2">
         <v>8.1000000000000013E-3</v>
       </c>
-      <c r="F362" s="32"/>
-      <c r="G362" s="32"/>
-      <c r="H362" s="2"/>
-      <c r="I362" s="2"/>
-      <c r="J362" s="6"/>
-      <c r="K362" s="7"/>
-    </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" s="5">
         <v>40575</v>
       </c>
@@ -9140,17 +6738,11 @@
       <c r="D363" s="2">
         <v>1.52E-2</v>
       </c>
-      <c r="E363" s="33">
+      <c r="E363" s="2">
         <v>1.09E-2</v>
       </c>
-      <c r="F363" s="32"/>
-      <c r="G363" s="32"/>
-      <c r="H363" s="2"/>
-      <c r="I363" s="2"/>
-      <c r="J363" s="6"/>
-      <c r="K363" s="7"/>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" s="5">
         <v>40603</v>
       </c>
@@ -9163,17 +6755,11 @@
       <c r="D364" s="2">
         <v>2.6000000000000002E-2</v>
       </c>
-      <c r="E364" s="33">
+      <c r="E364" s="2">
         <v>-1.55E-2</v>
       </c>
-      <c r="F364" s="32"/>
-      <c r="G364" s="32"/>
-      <c r="H364" s="2"/>
-      <c r="I364" s="2"/>
-      <c r="J364" s="6"/>
-      <c r="K364" s="7"/>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" s="5">
         <v>40634</v>
       </c>
@@ -9186,17 +6772,11 @@
       <c r="D365" s="2">
         <v>-3.4000000000000002E-3</v>
       </c>
-      <c r="E365" s="33">
+      <c r="E365" s="2">
         <v>-2.5099999999999997E-2</v>
       </c>
-      <c r="F365" s="32"/>
-      <c r="G365" s="32"/>
-      <c r="H365" s="2"/>
-      <c r="I365" s="2"/>
-      <c r="J365" s="6"/>
-      <c r="K365" s="7"/>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" s="5">
         <v>40664</v>
       </c>
@@ -9209,17 +6789,11 @@
       <c r="D366" s="2">
         <v>-6.9999999999999993E-3</v>
       </c>
-      <c r="E366" s="33">
+      <c r="E366" s="2">
         <v>-2.07E-2</v>
       </c>
-      <c r="F366" s="32"/>
-      <c r="G366" s="32"/>
-      <c r="H366" s="2"/>
-      <c r="I366" s="2"/>
-      <c r="J366" s="6"/>
-      <c r="K366" s="7"/>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" s="5">
         <v>40695</v>
       </c>
@@ -9232,17 +6806,11 @@
       <c r="D367" s="2">
         <v>-1.8E-3</v>
       </c>
-      <c r="E367" s="33">
+      <c r="E367" s="2">
         <v>-3.0999999999999999E-3</v>
       </c>
-      <c r="F367" s="32"/>
-      <c r="G367" s="32"/>
-      <c r="H367" s="2"/>
-      <c r="I367" s="2"/>
-      <c r="J367" s="6"/>
-      <c r="K367" s="7"/>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" s="5">
         <v>40725</v>
       </c>
@@ -9255,17 +6823,11 @@
       <c r="D368" s="2">
         <v>-1.3100000000000001E-2</v>
       </c>
-      <c r="E368" s="33">
+      <c r="E368" s="2">
         <v>-1.23E-2</v>
       </c>
-      <c r="F368" s="32"/>
-      <c r="G368" s="32"/>
-      <c r="H368" s="2"/>
-      <c r="I368" s="2"/>
-      <c r="J368" s="6"/>
-      <c r="K368" s="7"/>
-    </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" s="5">
         <v>40756</v>
       </c>
@@ -9278,17 +6840,11 @@
       <c r="D369" s="2">
         <v>-3.0600000000000002E-2</v>
       </c>
-      <c r="E369" s="33">
+      <c r="E369" s="2">
         <v>-2.4399999999999998E-2</v>
       </c>
-      <c r="F369" s="32"/>
-      <c r="G369" s="32"/>
-      <c r="H369" s="2"/>
-      <c r="I369" s="2"/>
-      <c r="J369" s="6"/>
-      <c r="K369" s="7"/>
-    </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" s="5">
         <v>40787</v>
       </c>
@@ -9301,17 +6857,11 @@
       <c r="D370" s="2">
         <v>-3.4799999999999998E-2</v>
       </c>
-      <c r="E370" s="33">
+      <c r="E370" s="2">
         <v>-1.46E-2</v>
       </c>
-      <c r="F370" s="32"/>
-      <c r="G370" s="32"/>
-      <c r="H370" s="2"/>
-      <c r="I370" s="2"/>
-      <c r="J370" s="6"/>
-      <c r="K370" s="7"/>
-    </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" s="5">
         <v>40817</v>
       </c>
@@ -9324,17 +6874,11 @@
       <c r="D371" s="2">
         <v>3.4099999999999998E-2</v>
       </c>
-      <c r="E371" s="33">
+      <c r="E371" s="2">
         <v>-1.7000000000000001E-3</v>
       </c>
-      <c r="F371" s="32"/>
-      <c r="G371" s="32"/>
-      <c r="H371" s="2"/>
-      <c r="I371" s="2"/>
-      <c r="J371" s="6"/>
-      <c r="K371" s="7"/>
-    </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" s="5">
         <v>40848</v>
       </c>
@@ -9347,17 +6891,11 @@
       <c r="D372" s="2">
         <v>-1.7000000000000001E-3</v>
       </c>
-      <c r="E372" s="33">
+      <c r="E372" s="2">
         <v>-3.4999999999999996E-3</v>
       </c>
-      <c r="F372" s="32"/>
-      <c r="G372" s="32"/>
-      <c r="H372" s="2"/>
-      <c r="I372" s="2"/>
-      <c r="J372" s="6"/>
-      <c r="K372" s="7"/>
-    </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" s="5">
         <v>40878</v>
       </c>
@@ -9370,17 +6908,11 @@
       <c r="D373" s="2">
         <v>-7.0999999999999995E-3</v>
       </c>
-      <c r="E373" s="33">
+      <c r="E373" s="2">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="F373" s="32"/>
-      <c r="G373" s="32"/>
-      <c r="H373" s="2"/>
-      <c r="I373" s="2"/>
-      <c r="J373" s="6"/>
-      <c r="K373" s="7"/>
-    </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" s="5">
         <v>40909</v>
       </c>
@@ -9393,17 +6925,11 @@
       <c r="D374" s="2">
         <v>2.1499999999999998E-2</v>
       </c>
-      <c r="E374" s="33">
+      <c r="E374" s="2">
         <v>-1.09E-2</v>
       </c>
-      <c r="F374" s="32"/>
-      <c r="G374" s="32"/>
-      <c r="H374" s="2"/>
-      <c r="I374" s="2"/>
-      <c r="J374" s="6"/>
-      <c r="K374" s="7"/>
-    </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" s="5">
         <v>40940</v>
       </c>
@@ -9416,17 +6942,11 @@
       <c r="D375" s="2">
         <v>-1.7500000000000002E-2</v>
       </c>
-      <c r="E375" s="33">
+      <c r="E375" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="F375" s="32"/>
-      <c r="G375" s="32"/>
-      <c r="H375" s="2"/>
-      <c r="I375" s="2"/>
-      <c r="J375" s="6"/>
-      <c r="K375" s="7"/>
-    </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" s="5">
         <v>40969</v>
       </c>
@@ -9439,17 +6959,11 @@
       <c r="D376" s="2">
         <v>-6.0999999999999995E-3</v>
       </c>
-      <c r="E376" s="33">
+      <c r="E376" s="2">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="F376" s="32"/>
-      <c r="G376" s="32"/>
-      <c r="H376" s="2"/>
-      <c r="I376" s="2"/>
-      <c r="J376" s="6"/>
-      <c r="K376" s="7"/>
-    </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" s="5">
         <v>41000</v>
       </c>
@@ -9462,17 +6976,11 @@
       <c r="D377" s="2">
         <v>-5.1999999999999998E-3</v>
       </c>
-      <c r="E377" s="33">
+      <c r="E377" s="2">
         <v>-4.6999999999999993E-3</v>
       </c>
-      <c r="F377" s="32"/>
-      <c r="G377" s="32"/>
-      <c r="H377" s="2"/>
-      <c r="I377" s="2"/>
-      <c r="J377" s="6"/>
-      <c r="K377" s="7"/>
-    </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" s="5">
         <v>41030</v>
       </c>
@@ -9485,17 +6993,11 @@
       <c r="D378" s="2">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="E378" s="33">
+      <c r="E378" s="2">
         <v>-6.1999999999999998E-3</v>
       </c>
-      <c r="F378" s="32"/>
-      <c r="G378" s="32"/>
-      <c r="H378" s="2"/>
-      <c r="I378" s="2"/>
-      <c r="J378" s="6"/>
-      <c r="K378" s="7"/>
-    </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379" s="5">
         <v>41061</v>
       </c>
@@ -9508,17 +7010,11 @@
       <c r="D379" s="2">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="E379" s="33">
+      <c r="E379" s="2">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="F379" s="32"/>
-      <c r="G379" s="32"/>
-      <c r="H379" s="2"/>
-      <c r="I379" s="2"/>
-      <c r="J379" s="6"/>
-      <c r="K379" s="7"/>
-    </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380" s="5">
         <v>41091</v>
       </c>
@@ -9531,17 +7027,11 @@
       <c r="D380" s="2">
         <v>-2.58E-2</v>
       </c>
-      <c r="E380" s="33">
+      <c r="E380" s="2">
         <v>-2.5000000000000001E-3</v>
       </c>
-      <c r="F380" s="32"/>
-      <c r="G380" s="32"/>
-      <c r="H380" s="2"/>
-      <c r="I380" s="2"/>
-      <c r="J380" s="6"/>
-      <c r="K380" s="7"/>
-    </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381" s="5">
         <v>41122</v>
       </c>
@@ -9554,17 +7044,11 @@
       <c r="D381" s="2">
         <v>4.0999999999999995E-3</v>
       </c>
-      <c r="E381" s="33">
+      <c r="E381" s="2">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F381" s="32"/>
-      <c r="G381" s="32"/>
-      <c r="H381" s="2"/>
-      <c r="I381" s="2"/>
-      <c r="J381" s="6"/>
-      <c r="K381" s="7"/>
-    </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382" s="5">
         <v>41153</v>
       </c>
@@ -9577,17 +7061,11 @@
       <c r="D382" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E382" s="33">
+      <c r="E382" s="2">
         <v>1.52E-2</v>
       </c>
-      <c r="F382" s="32"/>
-      <c r="G382" s="32"/>
-      <c r="H382" s="2"/>
-      <c r="I382" s="2"/>
-      <c r="J382" s="6"/>
-      <c r="K382" s="7"/>
-    </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383" s="5">
         <v>41183</v>
       </c>
@@ -9600,17 +7078,11 @@
       <c r="D383" s="2">
         <v>-1.1399999999999999E-2</v>
       </c>
-      <c r="E383" s="33">
+      <c r="E383" s="2">
         <v>3.7900000000000003E-2</v>
       </c>
-      <c r="F383" s="32"/>
-      <c r="G383" s="32"/>
-      <c r="H383" s="2"/>
-      <c r="I383" s="2"/>
-      <c r="J383" s="6"/>
-      <c r="K383" s="7"/>
-    </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384" s="5">
         <v>41214</v>
       </c>
@@ -9623,17 +7095,11 @@
       <c r="D384" s="2">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="E384" s="33">
+      <c r="E384" s="2">
         <v>-9.5999999999999992E-3</v>
       </c>
-      <c r="F384" s="32"/>
-      <c r="G384" s="32"/>
-      <c r="H384" s="2"/>
-      <c r="I384" s="2"/>
-      <c r="J384" s="6"/>
-      <c r="K384" s="7"/>
-    </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385" s="5">
         <v>41244</v>
       </c>
@@ -9646,17 +7112,11 @@
       <c r="D385" s="2">
         <v>1.47E-2</v>
       </c>
-      <c r="E385" s="33">
+      <c r="E385" s="2">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="F385" s="32"/>
-      <c r="G385" s="32"/>
-      <c r="H385" s="2"/>
-      <c r="I385" s="2"/>
-      <c r="J385" s="6"/>
-      <c r="K385" s="7"/>
-    </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386" s="5">
         <v>41275</v>
       </c>
@@ -9669,17 +7129,11 @@
       <c r="D386" s="2">
         <v>3.9000000000000003E-3</v>
       </c>
-      <c r="E386" s="33">
+      <c r="E386" s="2">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="F386" s="32"/>
-      <c r="G386" s="32"/>
-      <c r="H386" s="2"/>
-      <c r="I386" s="2"/>
-      <c r="J386" s="6"/>
-      <c r="K386" s="7"/>
-    </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387" s="5">
         <v>41306</v>
       </c>
@@ -9692,17 +7146,11 @@
       <c r="D387" s="2">
         <v>-4.5000000000000005E-3</v>
       </c>
-      <c r="E387" s="33">
+      <c r="E387" s="2">
         <v>0</v>
       </c>
-      <c r="F387" s="32"/>
-      <c r="G387" s="32"/>
-      <c r="H387" s="2"/>
-      <c r="I387" s="2"/>
-      <c r="J387" s="6"/>
-      <c r="K387" s="7"/>
-    </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A388" s="5">
         <v>41334</v>
       </c>
@@ -9715,17 +7163,11 @@
       <c r="D388" s="2">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="E388" s="33">
+      <c r="E388" s="2">
         <v>-2.5999999999999999E-3</v>
       </c>
-      <c r="F388" s="32"/>
-      <c r="G388" s="32"/>
-      <c r="H388" s="2"/>
-      <c r="I388" s="2"/>
-      <c r="J388" s="6"/>
-      <c r="K388" s="7"/>
-    </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A389" s="5">
         <v>41365</v>
       </c>
@@ -9738,17 +7180,11 @@
       <c r="D389" s="2">
         <v>-2.4399999999999998E-2</v>
       </c>
-      <c r="E389" s="33">
+      <c r="E389" s="2">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="F389" s="32"/>
-      <c r="G389" s="32"/>
-      <c r="H389" s="2"/>
-      <c r="I389" s="2"/>
-      <c r="J389" s="6"/>
-      <c r="K389" s="7"/>
-    </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390" s="5">
         <v>41395</v>
       </c>
@@ -9761,17 +7197,11 @@
       <c r="D390" s="2">
         <v>1.67E-2</v>
       </c>
-      <c r="E390" s="33">
+      <c r="E390" s="2">
         <v>2.5499999999999998E-2</v>
       </c>
-      <c r="F390" s="32"/>
-      <c r="G390" s="32"/>
-      <c r="H390" s="2"/>
-      <c r="I390" s="2"/>
-      <c r="J390" s="6"/>
-      <c r="K390" s="7"/>
-    </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A391" s="5">
         <v>41426</v>
       </c>
@@ -9784,17 +7214,11 @@
       <c r="D391" s="2">
         <v>1.2199999999999999E-2</v>
       </c>
-      <c r="E391" s="33">
+      <c r="E391" s="2">
         <v>-1.9E-3</v>
       </c>
-      <c r="F391" s="32"/>
-      <c r="G391" s="32"/>
-      <c r="H391" s="2"/>
-      <c r="I391" s="2"/>
-      <c r="J391" s="6"/>
-      <c r="K391" s="7"/>
-    </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A392" s="5">
         <v>41456</v>
       </c>
@@ -9807,17 +7231,11 @@
       <c r="D392" s="2">
         <v>1.8600000000000002E-2</v>
       </c>
-      <c r="E392" s="33">
+      <c r="E392" s="2">
         <v>5.5000000000000005E-3</v>
       </c>
-      <c r="F392" s="32"/>
-      <c r="G392" s="32"/>
-      <c r="H392" s="2"/>
-      <c r="I392" s="2"/>
-      <c r="J392" s="6"/>
-      <c r="K392" s="7"/>
-    </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A393" s="5">
         <v>41487</v>
       </c>
@@ -9830,17 +7248,11 @@
       <c r="D393" s="2">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E393" s="33">
+      <c r="E393" s="2">
         <v>-2.7799999999999998E-2</v>
       </c>
-      <c r="F393" s="32"/>
-      <c r="G393" s="32"/>
-      <c r="H393" s="2"/>
-      <c r="I393" s="2"/>
-      <c r="J393" s="6"/>
-      <c r="K393" s="7"/>
-    </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A394" s="5">
         <v>41518</v>
       </c>
@@ -9853,17 +7265,11 @@
       <c r="D394" s="2">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="E394" s="33">
+      <c r="E394" s="2">
         <v>-1.18E-2</v>
       </c>
-      <c r="F394" s="32"/>
-      <c r="G394" s="32"/>
-      <c r="H394" s="2"/>
-      <c r="I394" s="2"/>
-      <c r="J394" s="6"/>
-      <c r="K394" s="7"/>
-    </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A395" s="5">
         <v>41548</v>
       </c>
@@ -9876,17 +7282,11 @@
       <c r="D395" s="2">
         <v>-1.49E-2</v>
       </c>
-      <c r="E395" s="33">
+      <c r="E395" s="2">
         <v>1.15E-2</v>
       </c>
-      <c r="F395" s="32"/>
-      <c r="G395" s="32"/>
-      <c r="H395" s="2"/>
-      <c r="I395" s="2"/>
-      <c r="J395" s="6"/>
-      <c r="K395" s="7"/>
-    </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A396" s="5">
         <v>41579</v>
       </c>
@@ -9899,17 +7299,11 @@
       <c r="D396" s="2">
         <v>1.24E-2</v>
       </c>
-      <c r="E396" s="33">
+      <c r="E396" s="2">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="F396" s="32"/>
-      <c r="G396" s="32"/>
-      <c r="H396" s="2"/>
-      <c r="I396" s="2"/>
-      <c r="J396" s="6"/>
-      <c r="K396" s="7"/>
-    </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A397" s="5">
         <v>41609</v>
       </c>
@@ -9922,17 +7316,11 @@
       <c r="D397" s="2">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E397" s="33">
+      <c r="E397" s="2">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="F397" s="32"/>
-      <c r="G397" s="32"/>
-      <c r="H397" s="2"/>
-      <c r="I397" s="2"/>
-      <c r="J397" s="6"/>
-      <c r="K397" s="7"/>
-    </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A398" s="5">
         <v>41640</v>
       </c>
@@ -9945,17 +7333,11 @@
       <c r="D398" s="2">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="E398" s="33">
+      <c r="E398" s="2">
         <v>-2.0799999999999999E-2</v>
       </c>
-      <c r="F398" s="32"/>
-      <c r="G398" s="32"/>
-      <c r="H398" s="2"/>
-      <c r="I398" s="2"/>
-      <c r="J398" s="6"/>
-      <c r="K398" s="7"/>
-    </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A399" s="5">
         <v>41671</v>
       </c>
@@ -9968,17 +7350,11 @@
       <c r="D399" s="2">
         <v>3.3E-3</v>
       </c>
-      <c r="E399" s="33">
+      <c r="E399" s="2">
         <v>-3.9000000000000003E-3</v>
       </c>
-      <c r="F399" s="32"/>
-      <c r="G399" s="32"/>
-      <c r="H399" s="2"/>
-      <c r="I399" s="2"/>
-      <c r="J399" s="6"/>
-      <c r="K399" s="7"/>
-    </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A400" s="5">
         <v>41699</v>
       </c>
@@ -9991,17 +7367,11 @@
       <c r="D400" s="2">
         <v>-1.89E-2</v>
       </c>
-      <c r="E400" s="33">
+      <c r="E400" s="2">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="F400" s="32"/>
-      <c r="G400" s="32"/>
-      <c r="H400" s="2"/>
-      <c r="I400" s="2"/>
-      <c r="J400" s="6"/>
-      <c r="K400" s="7"/>
-    </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A401" s="5">
         <v>41730</v>
       </c>
@@ -10014,17 +7384,11 @@
       <c r="D401" s="2">
         <v>-4.2500000000000003E-2</v>
       </c>
-      <c r="E401" s="33">
+      <c r="E401" s="2">
         <v>1.1399999999999999E-2</v>
       </c>
-      <c r="F401" s="32"/>
-      <c r="G401" s="32"/>
-      <c r="H401" s="2"/>
-      <c r="I401" s="2"/>
-      <c r="J401" s="6"/>
-      <c r="K401" s="7"/>
-    </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A402" s="5">
         <v>41760</v>
       </c>
@@ -10037,17 +7401,11 @@
       <c r="D402" s="2">
         <v>-1.83E-2</v>
       </c>
-      <c r="E402" s="33">
+      <c r="E402" s="2">
         <v>-2.5999999999999999E-3</v>
       </c>
-      <c r="F402" s="32"/>
-      <c r="G402" s="32"/>
-      <c r="H402" s="2"/>
-      <c r="I402" s="2"/>
-      <c r="J402" s="6"/>
-      <c r="K402" s="7"/>
-    </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A403" s="5">
         <v>41791</v>
       </c>
@@ -10060,17 +7418,11 @@
       <c r="D403" s="2">
         <v>3.0600000000000002E-2</v>
       </c>
-      <c r="E403" s="33">
+      <c r="E403" s="2">
         <v>-7.4000000000000003E-3</v>
       </c>
-      <c r="F403" s="32"/>
-      <c r="G403" s="32"/>
-      <c r="H403" s="2"/>
-      <c r="I403" s="2"/>
-      <c r="J403" s="6"/>
-      <c r="K403" s="7"/>
-    </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A404" s="5">
         <v>41821</v>
       </c>
@@ -10083,17 +7435,11 @@
       <c r="D404" s="2">
         <v>-4.2300000000000004E-2</v>
       </c>
-      <c r="E404" s="33">
+      <c r="E404" s="2">
         <v>1E-4</v>
       </c>
-      <c r="F404" s="32"/>
-      <c r="G404" s="32"/>
-      <c r="H404" s="2"/>
-      <c r="I404" s="2"/>
-      <c r="J404" s="6"/>
-      <c r="K404" s="7"/>
-    </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A405" s="5">
         <v>41852</v>
       </c>
@@ -10106,17 +7452,11 @@
       <c r="D405" s="2">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="E405" s="33">
+      <c r="E405" s="2">
         <v>-5.6999999999999993E-3</v>
       </c>
-      <c r="F405" s="32"/>
-      <c r="G405" s="32"/>
-      <c r="H405" s="2"/>
-      <c r="I405" s="2"/>
-      <c r="J405" s="6"/>
-      <c r="K405" s="7"/>
-    </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A406" s="5">
         <v>41883</v>
       </c>
@@ -10129,17 +7469,11 @@
       <c r="D406" s="2">
         <v>-3.8199999999999998E-2</v>
       </c>
-      <c r="E406" s="33">
+      <c r="E406" s="2">
         <v>-1.2199999999999999E-2</v>
       </c>
-      <c r="F406" s="32"/>
-      <c r="G406" s="32"/>
-      <c r="H406" s="2"/>
-      <c r="I406" s="2"/>
-      <c r="J406" s="6"/>
-      <c r="K406" s="7"/>
-    </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A407" s="5">
         <v>41913</v>
       </c>
@@ -10152,17 +7486,11 @@
       <c r="D407" s="2">
         <v>4.2300000000000004E-2</v>
       </c>
-      <c r="E407" s="33">
+      <c r="E407" s="2">
         <v>-1.6899999999999998E-2</v>
       </c>
-      <c r="F407" s="32"/>
-      <c r="G407" s="32"/>
-      <c r="H407" s="2"/>
-      <c r="I407" s="2"/>
-      <c r="J407" s="6"/>
-      <c r="K407" s="7"/>
-    </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A408" s="5">
         <v>41944</v>
       </c>
@@ -10175,17 +7503,11 @@
       <c r="D408" s="2">
         <v>-2.06E-2</v>
       </c>
-      <c r="E408" s="33">
+      <c r="E408" s="2">
         <v>-2.9900000000000003E-2</v>
       </c>
-      <c r="F408" s="32"/>
-      <c r="G408" s="32"/>
-      <c r="H408" s="2"/>
-      <c r="I408" s="2"/>
-      <c r="J408" s="6"/>
-      <c r="K408" s="7"/>
-    </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A409" s="5">
         <v>41974</v>
       </c>
@@ -10198,17 +7520,11 @@
       <c r="D409" s="2">
         <v>2.5399999999999999E-2</v>
       </c>
-      <c r="E409" s="33">
+      <c r="E409" s="2">
         <v>2.07E-2</v>
       </c>
-      <c r="F409" s="32"/>
-      <c r="G409" s="32"/>
-      <c r="H409" s="2"/>
-      <c r="I409" s="2"/>
-      <c r="J409" s="6"/>
-      <c r="K409" s="7"/>
-    </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A410" s="5">
         <v>42005</v>
       </c>
@@ -10221,17 +7537,11 @@
       <c r="D410" s="2">
         <v>-5.6999999999999993E-3</v>
       </c>
-      <c r="E410" s="33">
+      <c r="E410" s="2">
         <v>-3.4700000000000002E-2</v>
       </c>
-      <c r="F410" s="32"/>
-      <c r="G410" s="32"/>
-      <c r="H410" s="2"/>
-      <c r="I410" s="2"/>
-      <c r="J410" s="6"/>
-      <c r="K410" s="7"/>
-    </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A411" s="5">
         <v>42036</v>
       </c>
@@ -10244,17 +7554,11 @@
       <c r="D411" s="2">
         <v>5.3E-3</v>
       </c>
-      <c r="E411" s="33">
+      <c r="E411" s="2">
         <v>-1.77E-2</v>
       </c>
-      <c r="F411" s="32"/>
-      <c r="G411" s="32"/>
-      <c r="H411" s="2"/>
-      <c r="I411" s="2"/>
-      <c r="J411" s="6"/>
-      <c r="K411" s="7"/>
-    </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A412" s="5">
         <v>42064</v>
       </c>
@@ -10267,17 +7571,11 @@
       <c r="D412" s="2">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="E412" s="33">
+      <c r="E412" s="2">
         <v>-4.5000000000000005E-3</v>
       </c>
-      <c r="F412" s="32"/>
-      <c r="G412" s="32"/>
-      <c r="H412" s="2"/>
-      <c r="I412" s="2"/>
-      <c r="J412" s="6"/>
-      <c r="K412" s="7"/>
-    </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A413" s="5">
         <v>42095</v>
       </c>
@@ -10290,17 +7588,11 @@
       <c r="D413" s="2">
         <v>-2.9700000000000001E-2</v>
       </c>
-      <c r="E413" s="33">
+      <c r="E413" s="2">
         <v>1.8500000000000003E-2</v>
       </c>
-      <c r="F413" s="32"/>
-      <c r="G413" s="32"/>
-      <c r="H413" s="2"/>
-      <c r="I413" s="2"/>
-      <c r="J413" s="6"/>
-      <c r="K413" s="7"/>
-    </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A414" s="5">
         <v>42125</v>
       </c>
@@ -10313,17 +7605,11 @@
       <c r="D414" s="2">
         <v>9.3999999999999986E-3</v>
       </c>
-      <c r="E414" s="33">
+      <c r="E414" s="2">
         <v>-1.3300000000000001E-2</v>
       </c>
-      <c r="F414" s="32"/>
-      <c r="G414" s="32"/>
-      <c r="H414" s="2"/>
-      <c r="I414" s="2"/>
-      <c r="J414" s="6"/>
-      <c r="K414" s="7"/>
-    </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A415" s="5">
         <v>42156</v>
       </c>
@@ -10336,17 +7622,11 @@
       <c r="D415" s="2">
         <v>2.81E-2</v>
       </c>
-      <c r="E415" s="33">
+      <c r="E415" s="2">
         <v>-8.1000000000000013E-3</v>
       </c>
-      <c r="F415" s="32"/>
-      <c r="G415" s="32"/>
-      <c r="H415" s="2"/>
-      <c r="I415" s="2"/>
-      <c r="J415" s="6"/>
-      <c r="K415" s="7"/>
-    </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A416" s="5">
         <v>42186</v>
       </c>
@@ -10359,17 +7639,11 @@
       <c r="D416" s="2">
         <v>-4.1500000000000002E-2</v>
       </c>
-      <c r="E416" s="33">
+      <c r="E416" s="2">
         <v>-4.1399999999999999E-2</v>
       </c>
-      <c r="F416" s="32"/>
-      <c r="G416" s="32"/>
-      <c r="H416" s="2"/>
-      <c r="I416" s="2"/>
-      <c r="J416" s="6"/>
-      <c r="K416" s="7"/>
-    </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A417" s="5">
         <v>42217</v>
       </c>
@@ -10382,17 +7656,11 @@
       <c r="D417" s="2">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="E417" s="33">
+      <c r="E417" s="2">
         <v>2.69E-2</v>
       </c>
-      <c r="F417" s="32"/>
-      <c r="G417" s="32"/>
-      <c r="H417" s="2"/>
-      <c r="I417" s="2"/>
-      <c r="J417" s="6"/>
-      <c r="K417" s="7"/>
-    </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A418" s="5">
         <v>42248</v>
       </c>
@@ -10405,17 +7673,11 @@
       <c r="D418" s="2">
         <v>-2.64E-2</v>
       </c>
-      <c r="E418" s="33">
+      <c r="E418" s="2">
         <v>5.3E-3</v>
       </c>
-      <c r="F418" s="32"/>
-      <c r="G418" s="32"/>
-      <c r="H418" s="2"/>
-      <c r="I418" s="2"/>
-      <c r="J418" s="6"/>
-      <c r="K418" s="7"/>
-    </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A419" s="5">
         <v>42278</v>
       </c>
@@ -10428,17 +7690,11 @@
       <c r="D419" s="2">
         <v>-1.9799999999999998E-2</v>
       </c>
-      <c r="E419" s="33">
+      <c r="E419" s="2">
         <v>-8.9999999999999998E-4</v>
       </c>
-      <c r="F419" s="32"/>
-      <c r="G419" s="32"/>
-      <c r="H419" s="2"/>
-      <c r="I419" s="2"/>
-      <c r="J419" s="6"/>
-      <c r="K419" s="7"/>
-    </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A420" s="5">
         <v>42309</v>
       </c>
@@ -10451,17 +7707,11 @@
       <c r="D420" s="2">
         <v>3.6400000000000002E-2</v>
       </c>
-      <c r="E420" s="33">
+      <c r="E420" s="2">
         <v>-5.1000000000000004E-3</v>
       </c>
-      <c r="F420" s="32"/>
-      <c r="G420" s="32"/>
-      <c r="H420" s="2"/>
-      <c r="I420" s="2"/>
-      <c r="J420" s="6"/>
-      <c r="K420" s="7"/>
-    </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A421" s="5">
         <v>42339</v>
       </c>
@@ -10474,17 +7724,11 @@
       <c r="D421" s="2">
         <v>-2.81E-2</v>
       </c>
-      <c r="E421" s="33">
+      <c r="E421" s="2">
         <v>-2.5699999999999997E-2</v>
       </c>
-      <c r="F421" s="32"/>
-      <c r="G421" s="32"/>
-      <c r="H421" s="2"/>
-      <c r="I421" s="2"/>
-      <c r="J421" s="6"/>
-      <c r="K421" s="7"/>
-    </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A422" s="5">
         <v>42370</v>
       </c>
@@ -10497,17 +7741,11 @@
       <c r="D422" s="2">
         <v>-3.39E-2</v>
       </c>
-      <c r="E422" s="33">
+      <c r="E422" s="2">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F422" s="32"/>
-      <c r="G422" s="32"/>
-      <c r="H422" s="2"/>
-      <c r="I422" s="2"/>
-      <c r="J422" s="6"/>
-      <c r="K422" s="7"/>
-    </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A423" s="5">
         <v>42401</v>
       </c>
@@ -10520,17 +7758,11 @@
       <c r="D423" s="2">
         <v>7.8000000000000005E-3</v>
       </c>
-      <c r="E423" s="33">
+      <c r="E423" s="2">
         <v>-4.7999999999999996E-3</v>
       </c>
-      <c r="F423" s="32"/>
-      <c r="G423" s="32"/>
-      <c r="H423" s="2"/>
-      <c r="I423" s="2"/>
-      <c r="J423" s="6"/>
-      <c r="K423" s="7"/>
-    </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A424" s="5">
         <v>42430</v>
       </c>
@@ -10543,17 +7775,11 @@
       <c r="D424" s="2">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="E424" s="33">
+      <c r="E424" s="2">
         <v>1.1399999999999999E-2</v>
       </c>
-      <c r="F424" s="32"/>
-      <c r="G424" s="32"/>
-      <c r="H424" s="2"/>
-      <c r="I424" s="2"/>
-      <c r="J424" s="6"/>
-      <c r="K424" s="7"/>
-    </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A425" s="5">
         <v>42461</v>
       </c>
@@ -10566,17 +7792,11 @@
       <c r="D425" s="2">
         <v>6.7000000000000002E-3</v>
       </c>
-      <c r="E425" s="33">
+      <c r="E425" s="2">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="F425" s="32"/>
-      <c r="G425" s="32"/>
-      <c r="H425" s="2"/>
-      <c r="I425" s="2"/>
-      <c r="J425" s="6"/>
-      <c r="K425" s="7"/>
-    </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A426" s="5">
         <v>42491</v>
       </c>
@@ -10589,17 +7809,11 @@
       <c r="D426" s="2">
         <v>-2.5999999999999999E-3</v>
       </c>
-      <c r="E426" s="33">
+      <c r="E426" s="2">
         <v>-1.8000000000000002E-2</v>
       </c>
-      <c r="F426" s="32"/>
-      <c r="G426" s="32"/>
-      <c r="H426" s="2"/>
-      <c r="I426" s="2"/>
-      <c r="J426" s="6"/>
-      <c r="K426" s="7"/>
-    </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A427" s="5">
         <v>42522</v>
       </c>
@@ -10612,17 +7826,11 @@
       <c r="D427" s="2">
         <v>6.5000000000000006E-3</v>
       </c>
-      <c r="E427" s="33">
+      <c r="E427" s="2">
         <v>-1.49E-2</v>
       </c>
-      <c r="F427" s="32"/>
-      <c r="G427" s="32"/>
-      <c r="H427" s="2"/>
-      <c r="I427" s="2"/>
-      <c r="J427" s="6"/>
-      <c r="K427" s="7"/>
-    </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A428" s="5">
         <v>42552</v>
       </c>
@@ -10635,17 +7843,11 @@
       <c r="D428" s="2">
         <v>2.64E-2</v>
       </c>
-      <c r="E428" s="33">
+      <c r="E428" s="2">
         <v>-1.1299999999999999E-2</v>
       </c>
-      <c r="F428" s="32"/>
-      <c r="G428" s="32"/>
-      <c r="H428" s="2"/>
-      <c r="I428" s="2"/>
-      <c r="J428" s="6"/>
-      <c r="K428" s="7"/>
-    </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A429" s="5">
         <v>42583</v>
       </c>
@@ -10658,17 +7860,11 @@
       <c r="D429" s="2">
         <v>1.1699999999999999E-2</v>
       </c>
-      <c r="E429" s="33">
+      <c r="E429" s="2">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="F429" s="32"/>
-      <c r="G429" s="32"/>
-      <c r="H429" s="2"/>
-      <c r="I429" s="2"/>
-      <c r="J429" s="6"/>
-      <c r="K429" s="7"/>
-    </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A430" s="5">
         <v>42614</v>
       </c>
@@ -10681,17 +7877,11 @@
       <c r="D430" s="2">
         <v>2.0099999999999996E-2</v>
       </c>
-      <c r="E430" s="33">
+      <c r="E430" s="2">
         <v>-1.49E-2</v>
       </c>
-      <c r="F430" s="32"/>
-      <c r="G430" s="32"/>
-      <c r="H430" s="2"/>
-      <c r="I430" s="2"/>
-      <c r="J430" s="6"/>
-      <c r="K430" s="7"/>
-    </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A431" s="5">
         <v>42644</v>
       </c>
@@ -10704,17 +7894,11 @@
       <c r="D431" s="2">
         <v>-4.36E-2</v>
       </c>
-      <c r="E431" s="33">
+      <c r="E431" s="2">
         <v>4.1599999999999998E-2</v>
       </c>
-      <c r="F431" s="32"/>
-      <c r="G431" s="32"/>
-      <c r="H431" s="2"/>
-      <c r="I431" s="2"/>
-      <c r="J431" s="6"/>
-      <c r="K431" s="7"/>
-    </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A432" s="5">
         <v>42675</v>
       </c>
@@ -10727,17 +7911,11 @@
       <c r="D432" s="2">
         <v>5.4800000000000001E-2</v>
       </c>
-      <c r="E432" s="33">
+      <c r="E432" s="2">
         <v>8.2699999999999996E-2</v>
       </c>
-      <c r="F432" s="32"/>
-      <c r="G432" s="32"/>
-      <c r="H432" s="2"/>
-      <c r="I432" s="2"/>
-      <c r="J432" s="6"/>
-      <c r="K432" s="7"/>
-    </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A433" s="5">
         <v>42705</v>
       </c>
@@ -10750,367 +7928,11 @@
       <c r="D433" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="E433" s="33">
+      <c r="E433" s="2">
         <v>3.61E-2</v>
       </c>
-      <c r="F433" s="32"/>
-      <c r="G433" s="32"/>
-      <c r="H433" s="2"/>
-      <c r="I433" s="2"/>
-      <c r="J433" s="6"/>
-      <c r="K433" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF30DA8D-D1D3-4FA9-9E64-DE242F48FD61}">
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
-  <cols>
-    <col min="1" max="1" width="15.59765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.69921875" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.25" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.9" thickBot="1" x14ac:dyDescent="0.65"/>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="14"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A5" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A6" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="17"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A7" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="18"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.9" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="20"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.9" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A10" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A12" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="18"/>
-      <c r="H12" s="24"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.9" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A14" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.9" thickBot="1" x14ac:dyDescent="0.65"/>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A17" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="16">
-        <v>1.3884184886749492E-2</v>
-      </c>
-      <c r="C17" s="16">
-        <v>5.7216257200284537E-3</v>
-      </c>
-      <c r="D17" s="16">
-        <v>2.4266153653057274</v>
-      </c>
-      <c r="E17" s="16">
-        <v>1.5652454930658633E-2</v>
-      </c>
-      <c r="F17" s="16">
-        <v>2.6382030004273339E-3</v>
-      </c>
-      <c r="G17" s="16">
-        <v>2.5130166773071651E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A18" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="16">
-        <v>1.2271958570952037</v>
-      </c>
-      <c r="C18" s="16">
-        <v>0.13289505124378864</v>
-      </c>
-      <c r="D18" s="16">
-        <v>9.2343232167763762</v>
-      </c>
-      <c r="E18" s="16">
-        <v>1.2169090262194339E-18</v>
-      </c>
-      <c r="F18" s="16">
-        <v>0.96598769490488312</v>
-      </c>
-      <c r="G18" s="16">
-        <v>1.4884040192855243</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A19" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="16">
-        <v>0.27864442829186514</v>
-      </c>
-      <c r="C19" s="16">
-        <v>0.19445569928008538</v>
-      </c>
-      <c r="D19" s="16">
-        <v>1.4329455465870302</v>
-      </c>
-      <c r="E19" s="16">
-        <v>0.15260341408919328</v>
-      </c>
-      <c r="F19" s="16">
-        <v>-0.10356254902595108</v>
-      </c>
-      <c r="G19" s="16">
-        <v>0.66085140560968136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.9" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A20" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" s="26">
-        <v>-0.90123358275343013</v>
-      </c>
-      <c r="C20" s="26">
-        <v>0.20395809011437729</v>
-      </c>
-      <c r="D20" s="26">
-        <v>-4.41871946461172</v>
-      </c>
-      <c r="E20" s="26">
-        <v>1.2596995618952944E-5</v>
-      </c>
-      <c r="F20" s="26">
-        <v>-1.302117719401177</v>
-      </c>
-      <c r="G20" s="26">
-        <v>-0.50034944610568322</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C66E602C-E5A8-4430-AE9B-F94B158334B0}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
-  <cols>
-    <col min="1" max="1" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.1484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.6484375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="29"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="29"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="29"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="27"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="27"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A15" s="24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="27"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="28"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="28"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B21:C21"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>